--- a/jomorais-backend/scratch/generated_pauta.xlsx
+++ b/jomorais-backend/scratch/generated_pauta.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="133">
   <si>
     <t>INSTITUTO TÉCNICO PRIVADO DE SAÚDE JOMORAIS</t>
   </si>
@@ -48,70 +48,94 @@
     <t>CURSO:</t>
   </si>
   <si>
+    <t>TRIMESTRE:</t>
+  </si>
+  <si>
+    <t>I TRIMESTRE</t>
+  </si>
+  <si>
+    <t>________________________________________</t>
+  </si>
+  <si>
+    <t>CLASSE:</t>
+  </si>
+  <si>
+    <t>10ª CLASSE</t>
+  </si>
+  <si>
+    <t>TURMA:</t>
+  </si>
+  <si>
+    <t>10ª ÚNICA-ANÁLISES CLÌNICAS-MATINAL</t>
+  </si>
+  <si>
+    <t>ALUNOS:</t>
+  </si>
+  <si>
+    <t>GABRIEL PRÓSPERO MABIALA</t>
+  </si>
+  <si>
+    <t>PERÍODO:</t>
+  </si>
+  <si>
+    <t>MANHA</t>
+  </si>
+  <si>
+    <t>ANO LECTIVO:</t>
+  </si>
+  <si>
+    <t>2022/2023</t>
+  </si>
+  <si>
+    <t>EMISSÃO:</t>
+  </si>
+  <si>
+    <t>07/06/26</t>
+  </si>
+  <si>
+    <t>DATA ______ / ______ / 2026</t>
+  </si>
+  <si>
+    <t>Nº</t>
+  </si>
+  <si>
+    <t>Nº PROC</t>
+  </si>
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>DISCIPLINA A REPETIR</t>
+  </si>
+  <si>
+    <t>ANATOMIA FISIOLOGIA HUMANA</t>
+  </si>
+  <si>
+    <t>BIOLOGIA</t>
+  </si>
+  <si>
+    <t>F.A.I</t>
+  </si>
+  <si>
+    <t>FÍSICA</t>
+  </si>
+  <si>
     <t>INFORMÁTICA</t>
   </si>
   <si>
-    <t>TRIMESTRE:</t>
-  </si>
-  <si>
-    <t>I TRIMESTRE</t>
-  </si>
-  <si>
-    <t>________________________________________</t>
-  </si>
-  <si>
-    <t>CLASSE:</t>
-  </si>
-  <si>
-    <t>13ªCLASSE</t>
-  </si>
-  <si>
-    <t>TURMA:</t>
-  </si>
-  <si>
-    <t>13ª INFORMÁTICA</t>
-  </si>
-  <si>
-    <t>ALUNOS:</t>
-  </si>
-  <si>
-    <t>GABRIEL PRÓSPERO MABIALA</t>
-  </si>
-  <si>
-    <t>PERÍODO:</t>
-  </si>
-  <si>
-    <t>TODO DIA</t>
-  </si>
-  <si>
-    <t>ANO LECTIVO:</t>
-  </si>
-  <si>
-    <t>2022/2023</t>
-  </si>
-  <si>
-    <t>EMISSÃO:</t>
-  </si>
-  <si>
-    <t>07/06/26</t>
-  </si>
-  <si>
-    <t>DATA ______ / ______ / 2026</t>
-  </si>
-  <si>
-    <t>Nº</t>
-  </si>
-  <si>
-    <t>Nº PROC</t>
-  </si>
-  <si>
-    <t>NOME</t>
-  </si>
-  <si>
-    <t>DISCIPLINA A REPETIR</t>
-  </si>
-  <si>
-    <t>PROJECTO TECNOLÓGICO</t>
+    <t>INTRODUÇÃO AO LABORATÓRIO</t>
+  </si>
+  <si>
+    <t>LÍNGUA INGLESA</t>
+  </si>
+  <si>
+    <t>LÍNGUA PORTUGUESA</t>
+  </si>
+  <si>
+    <t>MATEMÁTICA</t>
+  </si>
+  <si>
+    <t>QUÍMICA</t>
   </si>
   <si>
     <t>OBS</t>
@@ -159,28 +183,235 @@
     <t>F</t>
   </si>
   <si>
-    <t>OSVALDO SÉRGIO DUMBI SILVA</t>
-  </si>
-  <si>
-    <t>PROJE</t>
+    <t>SERGINA NVUMBI SIMBA</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>JOÃO KINHUMBA BAMENI</t>
-  </si>
-  <si>
-    <t>JOÃO SIMBA MBEUA MATIABA</t>
-  </si>
-  <si>
-    <t>SIMÃO PRECIL ZOLA</t>
-  </si>
-  <si>
-    <t>SILVÉRIO ERNESTO PRESO</t>
-  </si>
-  <si>
-    <t>SERAFIM CASSI MANANGA</t>
+    <t>SANDRA MIRANDA BUNGO</t>
+  </si>
+  <si>
+    <t>LÍNGU</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL BUANGA TATI</t>
+  </si>
+  <si>
+    <t>METELAS  ISSUNGO MACOSSO</t>
+  </si>
+  <si>
+    <t>F.A.I, FÍSIC</t>
+  </si>
+  <si>
+    <t>MARIA IMACULADA BANZA</t>
+  </si>
+  <si>
+    <t>MARIA MBENZA PACA GIMI</t>
+  </si>
+  <si>
+    <t>LÍNGU, QUÍMI</t>
+  </si>
+  <si>
+    <t>NASCIMENTO BARROS NSIMBA</t>
+  </si>
+  <si>
+    <t>MATEM</t>
+  </si>
+  <si>
+    <t>JOSÉ SILVESTRE DA CONCEIÇÃO DOMINGOS</t>
+  </si>
+  <si>
+    <t>MARIA DA RESSUREIÇÃO WINI MAVUNGO</t>
+  </si>
+  <si>
+    <t>ANATO</t>
+  </si>
+  <si>
+    <t>KELSON VICENTE BETE FRANCISCO</t>
+  </si>
+  <si>
+    <t>MARTA SUAMI LUEMBA MATOCO</t>
+  </si>
+  <si>
+    <t>LUÍSA BENEDITA PEMBA MBUMBA</t>
+  </si>
+  <si>
+    <t>BIOLO, INFOR</t>
+  </si>
+  <si>
+    <t>LUCIANO PALANGA MIGUEL</t>
+  </si>
+  <si>
+    <t>BIOLO</t>
+  </si>
+  <si>
+    <t>LÚCIA SUNGO CHIMKUMBO NDOKI</t>
+  </si>
+  <si>
+    <t>MARIA PRINCIPE CAPATA</t>
+  </si>
+  <si>
+    <t>MARGARIDA JOVANIA MACOSSO ZAU</t>
+  </si>
+  <si>
+    <t>MARIA CUMBA MALONDA NTÓTO</t>
+  </si>
+  <si>
+    <t>PERPÉTUA FERNANDA ZAU</t>
+  </si>
+  <si>
+    <t>MADALENA  BENVIDA CHINGOMBE LUEMBA</t>
+  </si>
+  <si>
+    <t>JOÃO GIME VULA</t>
+  </si>
+  <si>
+    <t>MADALENA TÂNIA BUMBA</t>
+  </si>
+  <si>
+    <t>TAMBA LANDO PONGO CASSINDA</t>
+  </si>
+  <si>
+    <t>QUÍMI</t>
+  </si>
+  <si>
+    <t>JOÃO PEDRO BÔNZELA</t>
+  </si>
+  <si>
+    <t>JULIETA MATAIA LANDO PAMBO</t>
+  </si>
+  <si>
+    <t>MARIA DOS ÂNJOS MADUCA PITRA</t>
+  </si>
+  <si>
+    <t>INFOR, MATEM</t>
+  </si>
+  <si>
+    <t>JOÃO JORGEE PEMBA PEQUENO</t>
+  </si>
+  <si>
+    <t>ROSA POMBO NGOMA</t>
+  </si>
+  <si>
+    <t>INTRO</t>
+  </si>
+  <si>
+    <t>IGOR MBEMBA NZAU</t>
+  </si>
+  <si>
+    <t>ISABEL DA FELICIDADE PEMBA MACAIA</t>
+  </si>
+  <si>
+    <t>HORVANDA ISABEL KOMBA NGAMI</t>
+  </si>
+  <si>
+    <t>EMILIANA VICTOR BAZA</t>
+  </si>
+  <si>
+    <t>EUNICE DIALA  SAXI</t>
+  </si>
+  <si>
+    <t>ELIANA BERNÍCIA PEMBA</t>
+  </si>
+  <si>
+    <t>ANATO, BIOLO, FÍSIC</t>
+  </si>
+  <si>
+    <t>CECILIA MALONDA NHITO</t>
+  </si>
+  <si>
+    <t>TERESA BUCA ESTEVÃO</t>
+  </si>
+  <si>
+    <t>INFOR</t>
+  </si>
+  <si>
+    <t>RUDELTA MOUILA MBUMBA</t>
+  </si>
+  <si>
+    <t>CLAÚDIA TERESA CUSTÓDIO BABACAIA</t>
+  </si>
+  <si>
+    <t>CRISTELA MENDES CONDE</t>
+  </si>
+  <si>
+    <t>CARLOS SIMÃO CUMBA</t>
+  </si>
+  <si>
+    <t>PAULINA BRÁS SAMBO BACOLA</t>
+  </si>
+  <si>
+    <t>CATARINA CUMBA SIMBA BUELA</t>
+  </si>
+  <si>
+    <t>BERNARDO ANTÓNIO KAPINGALO VICENTE</t>
+  </si>
+  <si>
+    <t>BEATRIZ RAMAZANA NGUEDI</t>
+  </si>
+  <si>
+    <t>ADELINA LANDO GOMES GIME</t>
+  </si>
+  <si>
+    <t>ADELINA GOMES MAMBUCO</t>
+  </si>
+  <si>
+    <t>ALFRASINA MUELA NGOMA LUBOTA</t>
+  </si>
+  <si>
+    <t>F.A.I, INTRO</t>
+  </si>
+  <si>
+    <t>ANTÓNIO CALENDE DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>ANA DA GRAÇA SOZINHO</t>
+  </si>
+  <si>
+    <t>HERMEGILDO FERNANDO CANDIEIRO</t>
+  </si>
+  <si>
+    <t>ANTÓNIO FELICIANO PEDRO ROCHA</t>
+  </si>
+  <si>
+    <t>ALBERTO PITRA SIMBA LUEMBA</t>
+  </si>
+  <si>
+    <t>ANTÓNIA DELFINA JOÃO</t>
+  </si>
+  <si>
+    <t>ALFA ANDRÉ MESSO</t>
+  </si>
+  <si>
+    <t>ALFREDO TULUNDA SAMBO</t>
+  </si>
+  <si>
+    <t>FÉNICA CONDE MAVUNGO</t>
+  </si>
+  <si>
+    <t>ALBERTO MIGUEL PRÓSPERO BAIONA</t>
+  </si>
+  <si>
+    <t>INTRO, QUÍMI</t>
+  </si>
+  <si>
+    <t>GERÓNIMO NHONGO TATI</t>
+  </si>
+  <si>
+    <t>ERNESTO ANTÓNIO DA COSTA CUMO</t>
+  </si>
+  <si>
+    <t>MADALENA BENVINDA CHINGOMBE LUEMBA</t>
+  </si>
+  <si>
+    <t>FÍSIC, LÍNGU</t>
+  </si>
+  <si>
+    <t>MARISA DA RESSUREIÇÃO WINI MAVUNGO</t>
+  </si>
+  <si>
+    <t>JORGETA DO CÉU DOMBE PIO.</t>
   </si>
   <si>
     <t>DATA DO CONSELHO DE TURMA ______ / ______ / 2026</t>
@@ -320,7 +551,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0070C0"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
@@ -338,7 +569,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF0070C0"/>
+      <color rgb="FFFF0000"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
@@ -450,7 +681,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -553,9 +784,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -959,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:T29"/>
+  <dimension ref="B1:AU84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -969,10 +1197,28 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="4" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="9" max="10" width="4" customWidth="1"/>
     <col min="11" max="11" width="7" customWidth="1"/>
-    <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="20" width="6" customWidth="1"/>
+    <col min="12" max="13" width="4" customWidth="1"/>
+    <col min="14" max="14" width="7" customWidth="1"/>
+    <col min="15" max="16" width="4" customWidth="1"/>
+    <col min="17" max="17" width="7" customWidth="1"/>
+    <col min="18" max="19" width="4" customWidth="1"/>
+    <col min="20" max="20" width="7" customWidth="1"/>
+    <col min="21" max="22" width="4" customWidth="1"/>
+    <col min="23" max="23" width="7" customWidth="1"/>
+    <col min="24" max="25" width="4" customWidth="1"/>
+    <col min="26" max="26" width="7" customWidth="1"/>
+    <col min="27" max="28" width="4" customWidth="1"/>
+    <col min="29" max="29" width="7" customWidth="1"/>
+    <col min="30" max="31" width="4" customWidth="1"/>
+    <col min="32" max="32" width="7" customWidth="1"/>
+    <col min="33" max="34" width="4" customWidth="1"/>
+    <col min="35" max="35" width="7" customWidth="1"/>
+    <col min="36" max="36" width="12" customWidth="1"/>
+    <col min="38" max="38" width="7" customWidth="1"/>
+    <col min="39" max="39" width="8" customWidth="1"/>
+    <col min="40" max="47" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1029,7 +1275,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" ht="18" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1051,6 +1297,33 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AL5" s="2"/>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
+      <c r="AU5" s="2"/>
     </row>
     <row r="6" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" ht="25" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -1106,7 +1379,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -1114,10 +1387,10 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="N10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="8" t="s">
         <v>7</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>8</v>
       </c>
       <c r="P10" s="8"/>
       <c r="Q10" s="8"/>
@@ -1125,30 +1398,30 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="F11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="13" t="s">
         <v>12</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>13</v>
       </c>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
       <c r="N11" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O11" s="14">
-        <f>CONCATENATE("Total: ", COUNTIF(L17:L22,"M")+COUNTIF(L17:L22,"F"), " (M: ", COUNTIF(L17:L22,"M"), ", F: ", COUNTIF(L17:L22,"F"), ")")</f>
+        <f>CONCATENATE("Total: ", COUNTIF(AM17:AM77,"M")+COUNTIF(AM17:AM77,"F"), " (M: ", COUNTIF(AM17:AM77,"M"), ", F: ", COUNTIF(AM17:AM77,"F"), ")")</f>
       </c>
       <c r="P11" s="14"/>
       <c r="Q11" s="14"/>
@@ -1156,30 +1429,30 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="F12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="17" t="s">
         <v>16</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>17</v>
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>19</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="N12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>20</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>21</v>
       </c>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
@@ -1187,458 +1460,7971 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
     </row>
-    <row r="14" ht="25" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" ht="25" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="D14" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="E14" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>26</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>27</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="L14" s="23" t="s">
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="M14" s="24" t="s">
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK14" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL14" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM14" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN14" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO14" s="24"/>
+      <c r="AP14" s="24"/>
+      <c r="AQ14" s="24"/>
+      <c r="AR14" s="24"/>
+      <c r="AS14" s="24"/>
+      <c r="AT14" s="24"/>
+      <c r="AU14" s="24"/>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" ht="18" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="25" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G15" s="25"/>
       <c r="H15" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" s="25"/>
+        <v>42</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="25"/>
+      <c r="K15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="M15" s="25"/>
+      <c r="N15" s="26" t="s">
+        <v>42</v>
+      </c>
       <c r="O15" s="25" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P15" s="25"/>
-      <c r="Q15" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="T15" s="25"/>
+      <c r="Q15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="S15" s="25"/>
+      <c r="T15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="V15" s="25"/>
+      <c r="W15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="X15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH15" s="25"/>
+      <c r="AI15" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ15" s="22"/>
+      <c r="AK15" s="22"/>
+      <c r="AL15" s="23"/>
+      <c r="AM15" s="23"/>
+      <c r="AN15" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AO15" s="25"/>
+      <c r="AP15" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ15" s="25"/>
+      <c r="AR15" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS15" s="25"/>
+      <c r="AT15" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU15" s="25"/>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
       <c r="F16" s="27" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H16" s="26"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="N16" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="P16" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q16" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="R16" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="S16" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="T16" s="25" t="s">
-        <v>42</v>
+      <c r="I16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="26"/>
+      <c r="L16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="M16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" s="26"/>
+      <c r="O16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="P16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="S16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="T16" s="26"/>
+      <c r="U16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="V16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="W16" s="26"/>
+      <c r="X16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC16" s="26"/>
+      <c r="AD16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI16" s="26"/>
+      <c r="AJ16" s="22"/>
+      <c r="AK16" s="22"/>
+      <c r="AL16" s="23"/>
+      <c r="AM16" s="23"/>
+      <c r="AN16" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO16" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP16" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AQ16" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR16" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS16" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT16" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU16" s="25" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B17" s="28">
         <v>1</v>
       </c>
       <c r="C17" s="28">
+        <v>714</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="I17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="L17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="28">
+        <v>3</v>
+      </c>
+      <c r="N17" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="O17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q17" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="R17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T17" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="U17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W17" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="X17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z17" s="32">
+        <v>13</v>
+      </c>
+      <c r="AA17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB17" s="28">
+        <v>4</v>
+      </c>
+      <c r="AC17" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="AD17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF17" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="AG17" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH17" s="28">
         <v>5</v>
       </c>
-      <c r="D17" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="30" t="s">
+      <c r="AI17" s="32">
+        <v>14.6</v>
+      </c>
+      <c r="AJ17" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="32">
-        <v>9.8</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="32">
-        <f>AVERAGE(H17)</f>
-      </c>
-      <c r="K17" s="28">
-        <v>23</v>
-      </c>
-      <c r="L17" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M17" s="34">
-        <f>COUNTIF(L17:L22,"M")</f>
-      </c>
-      <c r="N17" s="35">
-        <f>COUNTIF(L17:L22,"F")</f>
-      </c>
-      <c r="O17" s="34">
-        <f>COUNTIFS(I17:I22,"TRANSITA",L17:L22,"M")</f>
-      </c>
-      <c r="P17" s="35">
-        <f>COUNTIFS(I17:I22,"TRANSITA",L17:L22,"F")</f>
-      </c>
-      <c r="Q17" s="34">
-        <f>COUNTIFS(I17:I22,"N/TRANSITA",L17:L22,"M")</f>
-      </c>
-      <c r="R17" s="35">
-        <f>COUNTIFS(I17:I22,"N/TRANSITA",L17:L22,"F")</f>
-      </c>
-      <c r="S17" s="34">
-        <f>COUNTIFS(I17:I22,"DESISTIDO",L17:L22,"M")</f>
-      </c>
-      <c r="T17" s="35">
-        <f>COUNTIFS(I17:I22,"DESISTIDA",L17:L22,"F")</f>
+      <c r="AK17" s="32">
+        <f>AVERAGE(H17,K17,N17,Q17,T17,W17,Z17,AC17,AF17,AI17)</f>
+      </c>
+      <c r="AL17" s="28">
+        <v>22</v>
+      </c>
+      <c r="AM17" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN17" s="34">
+        <f>COUNTIF(AM17:AM77,"M")</f>
+      </c>
+      <c r="AO17" s="35">
+        <f>COUNTIF(AM17:AM77,"F")</f>
+      </c>
+      <c r="AP17" s="34">
+        <f>COUNTIFS(AJ17:AJ77,"TRANSITA",AM17:AM77,"M")</f>
+      </c>
+      <c r="AQ17" s="35">
+        <f>COUNTIFS(AJ17:AJ77,"TRANSITA",AM17:AM77,"F")</f>
+      </c>
+      <c r="AR17" s="34">
+        <f>COUNTIFS(AJ17:AJ77,"N/TRANSITA",AM17:AM77,"M")</f>
+      </c>
+      <c r="AS17" s="35">
+        <f>COUNTIFS(AJ17:AJ77,"N/TRANSITA",AM17:AM77,"F")</f>
+      </c>
+      <c r="AT17" s="34">
+        <f>COUNTIFS(AJ17:AJ77,"DESISTIDO",AM17:AM77,"M")</f>
+      </c>
+      <c r="AU17" s="35">
+        <f>COUNTIFS(AJ17:AJ77,"DESISTIDA",AM17:AM77,"F")</f>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B18" s="28">
         <v>2</v>
       </c>
       <c r="C18" s="28">
-        <v>7</v>
+        <v>1623</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" s="28">
-        <v>28</v>
-      </c>
-      <c r="L18" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M18" s="34"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="35"/>
+        <v>52</v>
+      </c>
+      <c r="H18" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N18" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="O18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q18" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="R18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T18" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="U18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V18" s="28">
+        <v>4</v>
+      </c>
+      <c r="W18" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="X18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z18" s="36">
+        <v>9.6</v>
+      </c>
+      <c r="AA18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB18" s="28">
+        <v>2</v>
+      </c>
+      <c r="AC18" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="AD18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF18" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="AG18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI18" s="32">
+        <v>16.5</v>
+      </c>
+      <c r="AJ18" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK18" s="32">
+        <f>AVERAGE(H18,K18,N18,Q18,T18,W18,Z18,AC18,AF18,AI18)</f>
+      </c>
+      <c r="AL18" s="28">
+        <v>22</v>
+      </c>
+      <c r="AM18" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN18" s="34"/>
+      <c r="AO18" s="35"/>
+      <c r="AP18" s="34"/>
+      <c r="AQ18" s="35"/>
+      <c r="AR18" s="34"/>
+      <c r="AS18" s="35"/>
+      <c r="AT18" s="34"/>
+      <c r="AU18" s="35"/>
     </row>
-    <row r="19" ht="20" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B19" s="28">
         <v>3</v>
       </c>
       <c r="C19" s="28">
-        <v>9</v>
+        <v>1625</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E19" s="30" t="s">
         <v>1</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="37">
+        <v>52</v>
+      </c>
+      <c r="H19" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="I19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="32">
+        <v>14</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="28">
+        <v>6</v>
+      </c>
+      <c r="N19" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="O19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P19" s="28">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="32">
         <v>14.2</v>
       </c>
-      <c r="I19" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="37">
-        <f>AVERAGE(H19)</f>
-      </c>
-      <c r="K19" s="28">
-        <v>23</v>
-      </c>
-      <c r="L19" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M19" s="34"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="35"/>
+      <c r="R19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T19" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="U19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W19" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="X19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z19" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="AA19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC19" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="AD19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF19" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="AG19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI19" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="AJ19" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK19" s="32">
+        <f>AVERAGE(H19,K19,N19,Q19,T19,W19,Z19,AC19,AF19,AI19)</f>
+      </c>
+      <c r="AL19" s="28">
+        <v>19</v>
+      </c>
+      <c r="AM19" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN19" s="34"/>
+      <c r="AO19" s="35"/>
+      <c r="AP19" s="34"/>
+      <c r="AQ19" s="35"/>
+      <c r="AR19" s="34"/>
+      <c r="AS19" s="35"/>
+      <c r="AT19" s="34"/>
+      <c r="AU19" s="35"/>
     </row>
-    <row r="20" ht="20" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B20" s="28">
         <v>4</v>
       </c>
       <c r="C20" s="28">
-        <v>10</v>
+        <v>1644</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="28">
-        <v>24</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M20" s="34"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="35"/>
+        <v>52</v>
+      </c>
+      <c r="G20" s="28">
+        <v>4</v>
+      </c>
+      <c r="H20" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="L20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="28">
+        <v>6</v>
+      </c>
+      <c r="N20" s="36">
+        <v>9.1</v>
+      </c>
+      <c r="O20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P20" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="36">
+        <v>9.6</v>
+      </c>
+      <c r="R20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T20" s="32">
+        <v>12</v>
+      </c>
+      <c r="U20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W20" s="32">
+        <v>14.7</v>
+      </c>
+      <c r="X20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z20" s="32">
+        <v>11.2</v>
+      </c>
+      <c r="AA20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC20" s="32">
+        <v>13.7</v>
+      </c>
+      <c r="AD20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF20" s="32">
+        <v>16.5</v>
+      </c>
+      <c r="AG20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI20" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="AJ20" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK20" s="32">
+        <f>AVERAGE(H20,K20,N20,Q20,T20,W20,Z20,AC20,AF20,AI20)</f>
+      </c>
+      <c r="AL20" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM20" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN20" s="34"/>
+      <c r="AO20" s="35"/>
+      <c r="AP20" s="34"/>
+      <c r="AQ20" s="35"/>
+      <c r="AR20" s="34"/>
+      <c r="AS20" s="35"/>
+      <c r="AT20" s="34"/>
+      <c r="AU20" s="35"/>
     </row>
-    <row r="21" ht="20" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B21" s="28">
         <v>5</v>
       </c>
       <c r="C21" s="28">
-        <v>1758</v>
+        <v>1645</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E21" s="30" t="s">
         <v>1</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="37">
-        <v>11</v>
-      </c>
-      <c r="I21" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="37">
-        <f>AVERAGE(H21)</f>
-      </c>
-      <c r="K21" s="28">
+        <v>52</v>
+      </c>
+      <c r="G21" s="28">
+        <v>5</v>
+      </c>
+      <c r="H21" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="O21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q21" s="32">
+        <v>15.3</v>
+      </c>
+      <c r="R21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S21" s="28">
+        <v>2</v>
+      </c>
+      <c r="T21" s="32">
+        <v>12.6</v>
+      </c>
+      <c r="U21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W21" s="32">
+        <v>14.3</v>
+      </c>
+      <c r="X21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z21" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="AA21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC21" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="AD21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF21" s="32">
+        <v>12.9</v>
+      </c>
+      <c r="AG21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI21" s="32">
+        <v>17.2</v>
+      </c>
+      <c r="AJ21" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK21" s="32">
+        <f>AVERAGE(H21,K21,N21,Q21,T21,W21,Z21,AC21,AF21,AI21)</f>
+      </c>
+      <c r="AL21" s="28">
         <v>26</v>
       </c>
-      <c r="L21" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" s="34"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="35"/>
+      <c r="AM21" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN21" s="34"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="34"/>
+      <c r="AQ21" s="35"/>
+      <c r="AR21" s="34"/>
+      <c r="AS21" s="35"/>
+      <c r="AT21" s="34"/>
+      <c r="AU21" s="35"/>
     </row>
-    <row r="22" ht="20" customHeight="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B22" s="28">
         <v>6</v>
       </c>
       <c r="C22" s="28">
-        <v>1771</v>
+        <v>1646</v>
       </c>
       <c r="D22" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="28">
+        <v>4</v>
+      </c>
+      <c r="H22" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K22" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="L22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N22" s="32">
+        <v>16.4</v>
+      </c>
+      <c r="O22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q22" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="R22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T22" s="32">
+        <v>10</v>
+      </c>
+      <c r="U22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V22" s="28">
+        <v>4</v>
+      </c>
+      <c r="W22" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="X22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z22" s="32">
+        <v>10.9</v>
+      </c>
+      <c r="AA22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC22" s="36">
+        <v>9.1</v>
+      </c>
+      <c r="AD22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF22" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="AG22" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH22" s="28">
+        <v>2</v>
+      </c>
+      <c r="AI22" s="36">
+        <v>8.9</v>
+      </c>
+      <c r="AJ22" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK22" s="32">
+        <f>AVERAGE(H22,K22,N22,Q22,T22,W22,Z22,AC22,AF22,AI22)</f>
+      </c>
+      <c r="AL22" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM22" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="AN22" s="34"/>
+      <c r="AO22" s="35"/>
+      <c r="AP22" s="34"/>
+      <c r="AQ22" s="35"/>
+      <c r="AR22" s="34"/>
+      <c r="AS22" s="35"/>
+      <c r="AT22" s="34"/>
+      <c r="AU22" s="35"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B23" s="28">
+        <v>7</v>
+      </c>
+      <c r="C23" s="28">
+        <v>1647</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="32">
+        <v>16.7</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K23" s="32">
+        <v>11.2</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N23" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="O23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P23" s="28">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="32">
+        <v>16.2</v>
+      </c>
+      <c r="R23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T23" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="U23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W23" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="X23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z23" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="AA23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC23" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="AD23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE23" s="28">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="36">
+        <v>9.1</v>
+      </c>
+      <c r="AG23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH23" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI23" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="AJ23" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK23" s="32">
+        <f>AVERAGE(H23,K23,N23,Q23,T23,W23,Z23,AC23,AF23,AI23)</f>
+      </c>
+      <c r="AL23" s="28">
+        <v>19</v>
+      </c>
+      <c r="AM23" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN23" s="34"/>
+      <c r="AO23" s="35"/>
+      <c r="AP23" s="34"/>
+      <c r="AQ23" s="35"/>
+      <c r="AR23" s="34"/>
+      <c r="AS23" s="35"/>
+      <c r="AT23" s="34"/>
+      <c r="AU23" s="35"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B24" s="28">
+        <v>8</v>
+      </c>
+      <c r="C24" s="28">
+        <v>1648</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="28">
+        <v>5</v>
+      </c>
+      <c r="H24" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K24" s="32">
+        <v>11</v>
+      </c>
+      <c r="L24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="28">
+        <v>6</v>
+      </c>
+      <c r="N24" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="O24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P24" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="R24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S24" s="28">
+        <v>5</v>
+      </c>
+      <c r="T24" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="U24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W24" s="32">
+        <v>11</v>
+      </c>
+      <c r="X24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z24" s="32">
+        <v>16</v>
+      </c>
+      <c r="AA24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC24" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="AD24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE24" s="28">
+        <v>3</v>
+      </c>
+      <c r="AF24" s="32">
+        <v>11</v>
+      </c>
+      <c r="AG24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH24" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI24" s="32">
+        <v>13</v>
+      </c>
+      <c r="AJ24" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK24" s="32">
+        <f>AVERAGE(H24,K24,N24,Q24,T24,W24,Z24,AC24,AF24,AI24)</f>
+      </c>
+      <c r="AL24" s="28">
+        <v>27</v>
+      </c>
+      <c r="AM24" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN24" s="34"/>
+      <c r="AO24" s="35"/>
+      <c r="AP24" s="34"/>
+      <c r="AQ24" s="35"/>
+      <c r="AR24" s="34"/>
+      <c r="AS24" s="35"/>
+      <c r="AT24" s="34"/>
+      <c r="AU24" s="35"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B25" s="28">
+        <v>9</v>
+      </c>
+      <c r="C25" s="28">
+        <v>1649</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="36">
+        <v>9.1</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K25" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="L25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M25" s="28">
+        <v>6</v>
+      </c>
+      <c r="N25" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="O25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q25" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="R25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S25" s="28">
+        <v>6</v>
+      </c>
+      <c r="T25" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="U25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W25" s="32">
+        <v>13</v>
+      </c>
+      <c r="X25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y25" s="28">
+        <v>3</v>
+      </c>
+      <c r="Z25" s="32">
+        <v>17.3</v>
+      </c>
+      <c r="AA25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC25" s="32">
+        <v>11.7</v>
+      </c>
+      <c r="AD25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF25" s="32">
+        <v>11</v>
+      </c>
+      <c r="AG25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH25" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI25" s="32">
+        <v>11.1</v>
+      </c>
+      <c r="AJ25" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK25" s="32">
+        <f>AVERAGE(H25,K25,N25,Q25,T25,W25,Z25,AC25,AF25,AI25)</f>
+      </c>
+      <c r="AL25" s="28">
+        <v>4</v>
+      </c>
+      <c r="AM25" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN25" s="34"/>
+      <c r="AO25" s="35"/>
+      <c r="AP25" s="34"/>
+      <c r="AQ25" s="35"/>
+      <c r="AR25" s="34"/>
+      <c r="AS25" s="35"/>
+      <c r="AT25" s="34"/>
+      <c r="AU25" s="35"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B26" s="28">
+        <v>10</v>
+      </c>
+      <c r="C26" s="28">
+        <v>1650</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="I26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="28">
+        <v>3</v>
+      </c>
+      <c r="K26" s="32">
+        <v>11.6</v>
+      </c>
+      <c r="L26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="28">
+        <v>2</v>
+      </c>
+      <c r="N26" s="32">
+        <v>15.1</v>
+      </c>
+      <c r="O26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q26" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="R26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T26" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="U26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W26" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="X26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z26" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="AA26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC26" s="36">
+        <v>9.1</v>
+      </c>
+      <c r="AD26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF26" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="AG26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI26" s="32">
+        <v>10</v>
+      </c>
+      <c r="AJ26" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK26" s="32">
+        <f>AVERAGE(H26,K26,N26,Q26,T26,W26,Z26,AC26,AF26,AI26)</f>
+      </c>
+      <c r="AL26" s="28">
+        <v>23</v>
+      </c>
+      <c r="AM26" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN26" s="34"/>
+      <c r="AO26" s="35"/>
+      <c r="AP26" s="34"/>
+      <c r="AQ26" s="35"/>
+      <c r="AR26" s="34"/>
+      <c r="AS26" s="35"/>
+      <c r="AT26" s="34"/>
+      <c r="AU26" s="35"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B27" s="28">
+        <v>11</v>
+      </c>
+      <c r="C27" s="28">
+        <v>1651</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M27" s="28">
+        <v>4</v>
+      </c>
+      <c r="N27" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="O27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P27" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="R27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S27" s="28">
+        <v>1</v>
+      </c>
+      <c r="T27" s="32">
+        <v>15.7</v>
+      </c>
+      <c r="U27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V27" s="28">
+        <v>4</v>
+      </c>
+      <c r="W27" s="32">
+        <v>13</v>
+      </c>
+      <c r="X27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z27" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="AA27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC27" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="AD27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF27" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="AG27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH27" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI27" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="AJ27" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK27" s="32">
+        <f>AVERAGE(H27,K27,N27,Q27,T27,W27,Z27,AC27,AF27,AI27)</f>
+      </c>
+      <c r="AL27" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM27" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN27" s="34"/>
+      <c r="AO27" s="35"/>
+      <c r="AP27" s="34"/>
+      <c r="AQ27" s="35"/>
+      <c r="AR27" s="34"/>
+      <c r="AS27" s="35"/>
+      <c r="AT27" s="34"/>
+      <c r="AU27" s="35"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B28" s="28">
+        <v>12</v>
+      </c>
+      <c r="C28" s="28">
+        <v>1652</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="28">
+        <v>3</v>
+      </c>
+      <c r="H28" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="36">
+        <v>9.9</v>
+      </c>
+      <c r="L28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N28" s="32">
+        <v>10.4</v>
+      </c>
+      <c r="O28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q28" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="R28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T28" s="36">
+        <v>9.9</v>
+      </c>
+      <c r="U28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W28" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="X28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z28" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="AA28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC28" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="AD28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE28" s="28">
+        <v>4</v>
+      </c>
+      <c r="AF28" s="32">
+        <v>13.7</v>
+      </c>
+      <c r="AG28" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH28" s="28">
+        <v>2</v>
+      </c>
+      <c r="AI28" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="AJ28" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK28" s="32">
+        <f>AVERAGE(H28,K28,N28,Q28,T28,W28,Z28,AC28,AF28,AI28)</f>
+      </c>
+      <c r="AL28" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM28" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN28" s="34"/>
+      <c r="AO28" s="35"/>
+      <c r="AP28" s="34"/>
+      <c r="AQ28" s="35"/>
+      <c r="AR28" s="34"/>
+      <c r="AS28" s="35"/>
+      <c r="AT28" s="34"/>
+      <c r="AU28" s="35"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B29" s="28">
+        <v>13</v>
+      </c>
+      <c r="C29" s="28">
+        <v>1653</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" s="32">
+        <v>16</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K29" s="36">
+        <v>9.3</v>
+      </c>
+      <c r="L29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N29" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="O29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P29" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="R29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T29" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="U29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W29" s="32">
+        <v>17.4</v>
+      </c>
+      <c r="X29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z29" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="AA29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC29" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AD29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE29" s="28">
+        <v>4</v>
+      </c>
+      <c r="AF29" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="AG29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI29" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="AJ29" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK29" s="32">
+        <f>AVERAGE(H29,K29,N29,Q29,T29,W29,Z29,AC29,AF29,AI29)</f>
+      </c>
+      <c r="AL29" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM29" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN29" s="34"/>
+      <c r="AO29" s="35"/>
+      <c r="AP29" s="34"/>
+      <c r="AQ29" s="35"/>
+      <c r="AR29" s="34"/>
+      <c r="AS29" s="35"/>
+      <c r="AT29" s="34"/>
+      <c r="AU29" s="35"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B30" s="28">
+        <v>14</v>
+      </c>
+      <c r="C30" s="28">
+        <v>1654</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="28">
+        <v>5</v>
+      </c>
+      <c r="H30" s="36">
+        <v>9.5</v>
+      </c>
+      <c r="I30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="28">
+        <v>1</v>
+      </c>
+      <c r="K30" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="L30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N30" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="O30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P30" s="28">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="R30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T30" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="U30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W30" s="32">
+        <v>15.9</v>
+      </c>
+      <c r="X30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z30" s="32">
+        <v>15.7</v>
+      </c>
+      <c r="AA30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC30" s="32">
+        <v>16.4</v>
+      </c>
+      <c r="AD30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF30" s="32">
+        <v>11.6</v>
+      </c>
+      <c r="AG30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH30" s="28">
+        <v>5</v>
+      </c>
+      <c r="AI30" s="32">
+        <v>12.6</v>
+      </c>
+      <c r="AJ30" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK30" s="32">
+        <f>AVERAGE(H30,K30,N30,Q30,T30,W30,Z30,AC30,AF30,AI30)</f>
+      </c>
+      <c r="AL30" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM30" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN30" s="34"/>
+      <c r="AO30" s="35"/>
+      <c r="AP30" s="34"/>
+      <c r="AQ30" s="35"/>
+      <c r="AR30" s="34"/>
+      <c r="AS30" s="35"/>
+      <c r="AT30" s="34"/>
+      <c r="AU30" s="35"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B31" s="28">
+        <v>15</v>
+      </c>
+      <c r="C31" s="28">
+        <v>1655</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="32">
+        <v>11.6</v>
+      </c>
+      <c r="L31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="28">
+        <v>4</v>
+      </c>
+      <c r="N31" s="32">
+        <v>11.2</v>
+      </c>
+      <c r="O31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P31" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="R31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T31" s="32">
+        <v>14.7</v>
+      </c>
+      <c r="U31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W31" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="X31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z31" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="AA31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC31" s="32">
+        <v>14.6</v>
+      </c>
+      <c r="AD31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE31" s="28">
+        <v>5</v>
+      </c>
+      <c r="AF31" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="AG31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH31" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI31" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="AJ31" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK31" s="32">
+        <f>AVERAGE(H31,K31,N31,Q31,T31,W31,Z31,AC31,AF31,AI31)</f>
+      </c>
+      <c r="AL31" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM31" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN31" s="34"/>
+      <c r="AO31" s="35"/>
+      <c r="AP31" s="34"/>
+      <c r="AQ31" s="35"/>
+      <c r="AR31" s="34"/>
+      <c r="AS31" s="35"/>
+      <c r="AT31" s="34"/>
+      <c r="AU31" s="35"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B32" s="28">
+        <v>16</v>
+      </c>
+      <c r="C32" s="28">
+        <v>1656</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32" s="28">
+        <v>2</v>
+      </c>
+      <c r="K32" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="L32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N32" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="O32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q32" s="32">
+        <v>11.6</v>
+      </c>
+      <c r="R32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S32" s="28">
+        <v>6</v>
+      </c>
+      <c r="T32" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="U32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V32" s="28">
+        <v>5</v>
+      </c>
+      <c r="W32" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="X32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z32" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="AA32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC32" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="AD32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF32" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="AG32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH32" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI32" s="32">
+        <v>17.9</v>
+      </c>
+      <c r="AJ32" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK32" s="32">
+        <f>AVERAGE(H32,K32,N32,Q32,T32,W32,Z32,AC32,AF32,AI32)</f>
+      </c>
+      <c r="AL32" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM32" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN32" s="34"/>
+      <c r="AO32" s="35"/>
+      <c r="AP32" s="34"/>
+      <c r="AQ32" s="35"/>
+      <c r="AR32" s="34"/>
+      <c r="AS32" s="35"/>
+      <c r="AT32" s="34"/>
+      <c r="AU32" s="35"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B33" s="28">
+        <v>17</v>
+      </c>
+      <c r="C33" s="28">
+        <v>1657</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="I33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K33" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="L33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N33" s="32">
+        <v>10.3</v>
+      </c>
+      <c r="O33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q33" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="R33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T33" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="U33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V33" s="28">
+        <v>4</v>
+      </c>
+      <c r="W33" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="X33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z33" s="32">
+        <v>15.1</v>
+      </c>
+      <c r="AA33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC33" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="AD33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF33" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="AG33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH33" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI33" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="AJ33" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK33" s="32">
+        <f>AVERAGE(H33,K33,N33,Q33,T33,W33,Z33,AC33,AF33,AI33)</f>
+      </c>
+      <c r="AL33" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM33" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN33" s="34"/>
+      <c r="AO33" s="35"/>
+      <c r="AP33" s="34"/>
+      <c r="AQ33" s="35"/>
+      <c r="AR33" s="34"/>
+      <c r="AS33" s="35"/>
+      <c r="AT33" s="34"/>
+      <c r="AU33" s="35"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B34" s="28">
+        <v>18</v>
+      </c>
+      <c r="C34" s="28">
+        <v>1658</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="I34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K34" s="36">
+        <v>9.8</v>
+      </c>
+      <c r="L34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N34" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="O34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q34" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="R34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S34" s="28">
+        <v>2</v>
+      </c>
+      <c r="T34" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="U34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V34" s="28">
+        <v>2</v>
+      </c>
+      <c r="W34" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="X34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z34" s="32">
+        <v>12</v>
+      </c>
+      <c r="AA34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC34" s="32">
+        <v>16.4</v>
+      </c>
+      <c r="AD34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF34" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="AG34" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH34" s="28">
+        <v>4</v>
+      </c>
+      <c r="AI34" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="AJ34" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK34" s="32">
+        <f>AVERAGE(H34,K34,N34,Q34,T34,W34,Z34,AC34,AF34,AI34)</f>
+      </c>
+      <c r="AL34" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM34" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN34" s="34"/>
+      <c r="AO34" s="35"/>
+      <c r="AP34" s="34"/>
+      <c r="AQ34" s="35"/>
+      <c r="AR34" s="34"/>
+      <c r="AS34" s="35"/>
+      <c r="AT34" s="34"/>
+      <c r="AU34" s="35"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B35" s="28">
+        <v>19</v>
+      </c>
+      <c r="C35" s="28">
+        <v>1659</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" s="32">
+        <v>16.4</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K35" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="L35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M35" s="28">
+        <v>3</v>
+      </c>
+      <c r="N35" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="O35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q35" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="R35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S35" s="28">
+        <v>6</v>
+      </c>
+      <c r="T35" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="U35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W35" s="32">
+        <v>15.3</v>
+      </c>
+      <c r="X35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y35" s="28">
+        <v>2</v>
+      </c>
+      <c r="Z35" s="32">
+        <v>15.7</v>
+      </c>
+      <c r="AA35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC35" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="AD35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF35" s="32">
+        <v>16.1</v>
+      </c>
+      <c r="AG35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH35" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI35" s="32">
+        <v>11</v>
+      </c>
+      <c r="AJ35" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK35" s="32">
+        <f>AVERAGE(H35,K35,N35,Q35,T35,W35,Z35,AC35,AF35,AI35)</f>
+      </c>
+      <c r="AL35" s="28">
+        <v>30</v>
+      </c>
+      <c r="AM35" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN35" s="34"/>
+      <c r="AO35" s="35"/>
+      <c r="AP35" s="34"/>
+      <c r="AQ35" s="35"/>
+      <c r="AR35" s="34"/>
+      <c r="AS35" s="35"/>
+      <c r="AT35" s="34"/>
+      <c r="AU35" s="35"/>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B36" s="28">
+        <v>20</v>
+      </c>
+      <c r="C36" s="28">
+        <v>1660</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="28">
+        <v>3</v>
+      </c>
+      <c r="K36" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="L36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M36" s="28">
+        <v>1</v>
+      </c>
+      <c r="N36" s="32">
+        <v>15</v>
+      </c>
+      <c r="O36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q36" s="32">
+        <v>17.5</v>
+      </c>
+      <c r="R36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T36" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="U36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W36" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="X36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z36" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="AA36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC36" s="32">
+        <v>15.3</v>
+      </c>
+      <c r="AD36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF36" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="AG36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH36" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI36" s="32">
+        <v>10.1</v>
+      </c>
+      <c r="AJ36" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK36" s="32">
+        <f>AVERAGE(H36,K36,N36,Q36,T36,W36,Z36,AC36,AF36,AI36)</f>
+      </c>
+      <c r="AL36" s="28">
+        <v>23</v>
+      </c>
+      <c r="AM36" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN36" s="34"/>
+      <c r="AO36" s="35"/>
+      <c r="AP36" s="34"/>
+      <c r="AQ36" s="35"/>
+      <c r="AR36" s="34"/>
+      <c r="AS36" s="35"/>
+      <c r="AT36" s="34"/>
+      <c r="AU36" s="35"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B37" s="28">
+        <v>21</v>
+      </c>
+      <c r="C37" s="28">
+        <v>1661</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H37" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="I37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K37" s="32">
+        <v>13</v>
+      </c>
+      <c r="L37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N37" s="32">
+        <v>15.5</v>
+      </c>
+      <c r="O37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q37" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="R37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T37" s="32">
+        <v>15.9</v>
+      </c>
+      <c r="U37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W37" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="X37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z37" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="AA37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB37" s="28">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="AD37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF37" s="32">
+        <v>15.5</v>
+      </c>
+      <c r="AG37" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH37" s="28">
+        <v>2</v>
+      </c>
+      <c r="AI37" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="AJ37" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK37" s="32">
+        <f>AVERAGE(H37,K37,N37,Q37,T37,W37,Z37,AC37,AF37,AI37)</f>
+      </c>
+      <c r="AL37" s="28">
+        <v>29</v>
+      </c>
+      <c r="AM37" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN37" s="34"/>
+      <c r="AO37" s="35"/>
+      <c r="AP37" s="34"/>
+      <c r="AQ37" s="35"/>
+      <c r="AR37" s="34"/>
+      <c r="AS37" s="35"/>
+      <c r="AT37" s="34"/>
+      <c r="AU37" s="35"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B38" s="28">
+        <v>22</v>
+      </c>
+      <c r="C38" s="28">
+        <v>1662</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K38" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="L38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="28">
+        <v>1</v>
+      </c>
+      <c r="N38" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="O38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q38" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="R38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T38" s="32">
+        <v>17.2</v>
+      </c>
+      <c r="U38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W38" s="32">
+        <v>11.2</v>
+      </c>
+      <c r="X38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y38" s="28">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="32">
+        <v>16.2</v>
+      </c>
+      <c r="AA38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC38" s="32">
+        <v>13</v>
+      </c>
+      <c r="AD38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE38" s="28">
+        <v>2</v>
+      </c>
+      <c r="AF38" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="AG38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH38" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI38" s="36">
+        <v>8.9</v>
+      </c>
+      <c r="AJ38" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK38" s="32">
+        <f>AVERAGE(H38,K38,N38,Q38,T38,W38,Z38,AC38,AF38,AI38)</f>
+      </c>
+      <c r="AL38" s="28">
+        <v>19</v>
+      </c>
+      <c r="AM38" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN38" s="34"/>
+      <c r="AO38" s="35"/>
+      <c r="AP38" s="34"/>
+      <c r="AQ38" s="35"/>
+      <c r="AR38" s="34"/>
+      <c r="AS38" s="35"/>
+      <c r="AT38" s="34"/>
+      <c r="AU38" s="35"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B39" s="28">
+        <v>23</v>
+      </c>
+      <c r="C39" s="28">
+        <v>1663</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" s="36">
+        <v>9.7</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J39" s="28">
+        <v>4</v>
+      </c>
+      <c r="K39" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="L39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N39" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="O39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q39" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="R39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S39" s="28">
+        <v>2</v>
+      </c>
+      <c r="T39" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="U39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V39" s="28">
+        <v>5</v>
+      </c>
+      <c r="W39" s="32">
+        <v>10.9</v>
+      </c>
+      <c r="X39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z39" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="AA39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC39" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AD39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE39" s="28">
+        <v>6</v>
+      </c>
+      <c r="AF39" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="AG39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH39" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI39" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="AJ39" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK39" s="32">
+        <f>AVERAGE(H39,K39,N39,Q39,T39,W39,Z39,AC39,AF39,AI39)</f>
+      </c>
+      <c r="AL39" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM39" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN39" s="34"/>
+      <c r="AO39" s="35"/>
+      <c r="AP39" s="34"/>
+      <c r="AQ39" s="35"/>
+      <c r="AR39" s="34"/>
+      <c r="AS39" s="35"/>
+      <c r="AT39" s="34"/>
+      <c r="AU39" s="35"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B40" s="28">
+        <v>24</v>
+      </c>
+      <c r="C40" s="28">
+        <v>1664</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="28">
+        <v>3</v>
+      </c>
+      <c r="H40" s="32">
+        <v>10.1</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" s="28">
+        <v>3</v>
+      </c>
+      <c r="K40" s="32">
+        <v>13</v>
+      </c>
+      <c r="L40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N40" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="O40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P40" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="R40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T40" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="U40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W40" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="X40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z40" s="32">
+        <v>15</v>
+      </c>
+      <c r="AA40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC40" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="AD40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE40" s="28">
+        <v>6</v>
+      </c>
+      <c r="AF40" s="32">
+        <v>14.3</v>
+      </c>
+      <c r="AG40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH40" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI40" s="32">
+        <v>16.9</v>
+      </c>
+      <c r="AJ40" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK40" s="32">
+        <f>AVERAGE(H40,K40,N40,Q40,T40,W40,Z40,AC40,AF40,AI40)</f>
+      </c>
+      <c r="AL40" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM40" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN40" s="34"/>
+      <c r="AO40" s="35"/>
+      <c r="AP40" s="34"/>
+      <c r="AQ40" s="35"/>
+      <c r="AR40" s="34"/>
+      <c r="AS40" s="35"/>
+      <c r="AT40" s="34"/>
+      <c r="AU40" s="35"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B41" s="28">
+        <v>25</v>
+      </c>
+      <c r="C41" s="28">
+        <v>1665</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="I41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K41" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="L41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="O41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P41" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="32">
+        <v>12.9</v>
+      </c>
+      <c r="R41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T41" s="36">
+        <v>9.9</v>
+      </c>
+      <c r="U41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V41" s="28">
+        <v>4</v>
+      </c>
+      <c r="W41" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="X41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z41" s="32">
+        <v>12.6</v>
+      </c>
+      <c r="AA41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB41" s="28">
+        <v>2</v>
+      </c>
+      <c r="AC41" s="32">
+        <v>16.7</v>
+      </c>
+      <c r="AD41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF41" s="36">
+        <v>9.5</v>
+      </c>
+      <c r="AG41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH41" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI41" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="AJ41" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK41" s="32">
+        <f>AVERAGE(H41,K41,N41,Q41,T41,W41,Z41,AC41,AF41,AI41)</f>
+      </c>
+      <c r="AL41" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM41" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN41" s="34"/>
+      <c r="AO41" s="35"/>
+      <c r="AP41" s="34"/>
+      <c r="AQ41" s="35"/>
+      <c r="AR41" s="34"/>
+      <c r="AS41" s="35"/>
+      <c r="AT41" s="34"/>
+      <c r="AU41" s="35"/>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B42" s="28">
+        <v>26</v>
+      </c>
+      <c r="C42" s="28">
+        <v>1666</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="28">
+        <v>4</v>
+      </c>
+      <c r="H42" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J42" s="28">
+        <v>4</v>
+      </c>
+      <c r="K42" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="L42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M42" s="28">
+        <v>2</v>
+      </c>
+      <c r="N42" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="O42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P42" s="28">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="R42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T42" s="32">
+        <v>14.7</v>
+      </c>
+      <c r="U42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V42" s="28">
+        <v>4</v>
+      </c>
+      <c r="W42" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="X42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z42" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="AA42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC42" s="32">
+        <v>16.2</v>
+      </c>
+      <c r="AD42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF42" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="AG42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH42" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI42" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AJ42" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK42" s="32">
+        <f>AVERAGE(H42,K42,N42,Q42,T42,W42,Z42,AC42,AF42,AI42)</f>
+      </c>
+      <c r="AL42" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM42" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN42" s="34"/>
+      <c r="AO42" s="35"/>
+      <c r="AP42" s="34"/>
+      <c r="AQ42" s="35"/>
+      <c r="AR42" s="34"/>
+      <c r="AS42" s="35"/>
+      <c r="AT42" s="34"/>
+      <c r="AU42" s="35"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B43" s="28">
+        <v>27</v>
+      </c>
+      <c r="C43" s="28">
+        <v>1667</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" s="32">
+        <v>13</v>
+      </c>
+      <c r="I43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J43" s="28">
+        <v>1</v>
+      </c>
+      <c r="K43" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="L43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N43" s="32">
+        <v>10.3</v>
+      </c>
+      <c r="O43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q43" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="R43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T43" s="32">
+        <v>15</v>
+      </c>
+      <c r="U43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W43" s="36">
+        <v>8.8</v>
+      </c>
+      <c r="X43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z43" s="32">
+        <v>15.7</v>
+      </c>
+      <c r="AA43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB43" s="28">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="AD43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF43" s="32">
+        <v>12.6</v>
+      </c>
+      <c r="AG43" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH43" s="28">
+        <v>4</v>
+      </c>
+      <c r="AI43" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="AJ43" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK43" s="32">
+        <f>AVERAGE(H43,K43,N43,Q43,T43,W43,Z43,AC43,AF43,AI43)</f>
+      </c>
+      <c r="AL43" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM43" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN43" s="34"/>
+      <c r="AO43" s="35"/>
+      <c r="AP43" s="34"/>
+      <c r="AQ43" s="35"/>
+      <c r="AR43" s="34"/>
+      <c r="AS43" s="35"/>
+      <c r="AT43" s="34"/>
+      <c r="AU43" s="35"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B44" s="28">
+        <v>28</v>
+      </c>
+      <c r="C44" s="28">
+        <v>1668</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="I44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J44" s="28">
+        <v>4</v>
+      </c>
+      <c r="K44" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="L44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N44" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="O44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P44" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q44" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="R44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T44" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="U44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V44" s="28">
+        <v>4</v>
+      </c>
+      <c r="W44" s="32">
+        <v>16.1</v>
+      </c>
+      <c r="X44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z44" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="AA44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC44" s="32">
+        <v>14.3</v>
+      </c>
+      <c r="AD44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF44" s="32">
+        <v>10</v>
+      </c>
+      <c r="AG44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH44" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI44" s="32">
+        <v>12.9</v>
+      </c>
+      <c r="AJ44" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK44" s="32">
+        <f>AVERAGE(H44,K44,N44,Q44,T44,W44,Z44,AC44,AF44,AI44)</f>
+      </c>
+      <c r="AL44" s="28">
+        <v>26</v>
+      </c>
+      <c r="AM44" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN44" s="34"/>
+      <c r="AO44" s="35"/>
+      <c r="AP44" s="34"/>
+      <c r="AQ44" s="35"/>
+      <c r="AR44" s="34"/>
+      <c r="AS44" s="35"/>
+      <c r="AT44" s="34"/>
+      <c r="AU44" s="35"/>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B45" s="28">
+        <v>29</v>
+      </c>
+      <c r="C45" s="28">
+        <v>1669</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="I45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K45" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="L45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N45" s="32">
+        <v>11.6</v>
+      </c>
+      <c r="O45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q45" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="R45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T45" s="32">
+        <v>10</v>
+      </c>
+      <c r="U45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W45" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="X45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z45" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="AA45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB45" s="28">
+        <v>2</v>
+      </c>
+      <c r="AC45" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="AD45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF45" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="AG45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH45" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI45" s="32">
+        <v>13.7</v>
+      </c>
+      <c r="AJ45" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK45" s="32">
+        <f>AVERAGE(H45,K45,N45,Q45,T45,W45,Z45,AC45,AF45,AI45)</f>
+      </c>
+      <c r="AL45" s="28">
+        <v>28</v>
+      </c>
+      <c r="AM45" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN45" s="34"/>
+      <c r="AO45" s="35"/>
+      <c r="AP45" s="34"/>
+      <c r="AQ45" s="35"/>
+      <c r="AR45" s="34"/>
+      <c r="AS45" s="35"/>
+      <c r="AT45" s="34"/>
+      <c r="AU45" s="35"/>
+    </row>
+    <row r="46" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B46" s="28">
+        <v>30</v>
+      </c>
+      <c r="C46" s="28">
+        <v>1670</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H46" s="32">
+        <v>12.9</v>
+      </c>
+      <c r="I46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K46" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="L46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N46" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="O46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P46" s="28">
+        <v>6</v>
+      </c>
+      <c r="Q46" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="R46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S46" s="28">
+        <v>2</v>
+      </c>
+      <c r="T46" s="32">
+        <v>15</v>
+      </c>
+      <c r="U46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W46" s="32">
+        <v>14</v>
+      </c>
+      <c r="X46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z46" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="AA46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC46" s="36">
+        <v>8.7</v>
+      </c>
+      <c r="AD46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF46" s="32">
+        <v>14.6</v>
+      </c>
+      <c r="AG46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH46" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI46" s="32">
+        <v>10.3</v>
+      </c>
+      <c r="AJ46" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK46" s="32">
+        <f>AVERAGE(H46,K46,N46,Q46,T46,W46,Z46,AC46,AF46,AI46)</f>
+      </c>
+      <c r="AL46" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM46" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN46" s="34"/>
+      <c r="AO46" s="35"/>
+      <c r="AP46" s="34"/>
+      <c r="AQ46" s="35"/>
+      <c r="AR46" s="34"/>
+      <c r="AS46" s="35"/>
+      <c r="AT46" s="34"/>
+      <c r="AU46" s="35"/>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B47" s="28">
+        <v>31</v>
+      </c>
+      <c r="C47" s="28">
+        <v>1671</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H47" s="32">
+        <v>16.5</v>
+      </c>
+      <c r="I47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J47" s="28">
+        <v>5</v>
+      </c>
+      <c r="K47" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="L47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N47" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="O47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q47" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="R47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T47" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="U47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W47" s="36">
+        <v>9.7</v>
+      </c>
+      <c r="X47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z47" s="32">
+        <v>16.6</v>
+      </c>
+      <c r="AA47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC47" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="AD47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE47" s="28">
+        <v>3</v>
+      </c>
+      <c r="AF47" s="32">
+        <v>15.5</v>
+      </c>
+      <c r="AG47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH47" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI47" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="AJ47" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK47" s="32">
+        <f>AVERAGE(H47,K47,N47,Q47,T47,W47,Z47,AC47,AF47,AI47)</f>
+      </c>
+      <c r="AL47" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM47" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN47" s="34"/>
+      <c r="AO47" s="35"/>
+      <c r="AP47" s="34"/>
+      <c r="AQ47" s="35"/>
+      <c r="AR47" s="34"/>
+      <c r="AS47" s="35"/>
+      <c r="AT47" s="34"/>
+      <c r="AU47" s="35"/>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B48" s="28">
+        <v>32</v>
+      </c>
+      <c r="C48" s="28">
+        <v>1672</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H48" s="32">
+        <v>10.4</v>
+      </c>
+      <c r="I48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K48" s="32">
+        <v>11</v>
+      </c>
+      <c r="L48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N48" s="32">
+        <v>14.3</v>
+      </c>
+      <c r="O48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q48" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="R48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T48" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="U48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W48" s="32">
+        <v>17.1</v>
+      </c>
+      <c r="X48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z48" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="AA48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC48" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="AD48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF48" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="AG48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH48" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI48" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="AJ48" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK48" s="32">
+        <f>AVERAGE(H48,K48,N48,Q48,T48,W48,Z48,AC48,AF48,AI48)</f>
+      </c>
+      <c r="AL48" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM48" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN48" s="34"/>
+      <c r="AO48" s="35"/>
+      <c r="AP48" s="34"/>
+      <c r="AQ48" s="35"/>
+      <c r="AR48" s="34"/>
+      <c r="AS48" s="35"/>
+      <c r="AT48" s="34"/>
+      <c r="AU48" s="35"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B49" s="28">
+        <v>33</v>
+      </c>
+      <c r="C49" s="28">
+        <v>1673</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H49" s="36">
+        <v>9.7</v>
+      </c>
+      <c r="I49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K49" s="36">
+        <v>9.7</v>
+      </c>
+      <c r="L49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N49" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="O49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P49" s="28">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="36">
+        <v>9.4</v>
+      </c>
+      <c r="R49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T49" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="U49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W49" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="X49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z49" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="AA49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB49" s="28">
+        <v>3</v>
+      </c>
+      <c r="AC49" s="32">
+        <v>13</v>
+      </c>
+      <c r="AD49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF49" s="32">
+        <v>15.7</v>
+      </c>
+      <c r="AG49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH49" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI49" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="AJ49" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="AK49" s="32">
+        <f>AVERAGE(H49,K49,N49,Q49,T49,W49,Z49,AC49,AF49,AI49)</f>
+      </c>
+      <c r="AL49" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM49" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN49" s="34"/>
+      <c r="AO49" s="35"/>
+      <c r="AP49" s="34"/>
+      <c r="AQ49" s="35"/>
+      <c r="AR49" s="34"/>
+      <c r="AS49" s="35"/>
+      <c r="AT49" s="34"/>
+      <c r="AU49" s="35"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B50" s="28">
+        <v>34</v>
+      </c>
+      <c r="C50" s="28">
+        <v>1674</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G50" s="28">
+        <v>3</v>
+      </c>
+      <c r="H50" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="I50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J50" s="28">
+        <v>3</v>
+      </c>
+      <c r="K50" s="32">
+        <v>13</v>
+      </c>
+      <c r="L50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M50" s="28">
+        <v>5</v>
+      </c>
+      <c r="N50" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="O50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q50" s="32">
+        <v>12.9</v>
+      </c>
+      <c r="R50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T50" s="32">
+        <v>15.2</v>
+      </c>
+      <c r="U50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W50" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="X50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z50" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="AA50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC50" s="36">
+        <v>9.4</v>
+      </c>
+      <c r="AD50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF50" s="32">
+        <v>16.3</v>
+      </c>
+      <c r="AG50" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH50" s="28">
+        <v>6</v>
+      </c>
+      <c r="AI50" s="32">
+        <v>16</v>
+      </c>
+      <c r="AJ50" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK50" s="32">
+        <f>AVERAGE(H50,K50,N50,Q50,T50,W50,Z50,AC50,AF50,AI50)</f>
+      </c>
+      <c r="AL50" s="28">
+        <v>22</v>
+      </c>
+      <c r="AM50" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN50" s="34"/>
+      <c r="AO50" s="35"/>
+      <c r="AP50" s="34"/>
+      <c r="AQ50" s="35"/>
+      <c r="AR50" s="34"/>
+      <c r="AS50" s="35"/>
+      <c r="AT50" s="34"/>
+      <c r="AU50" s="35"/>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B51" s="28">
+        <v>35</v>
+      </c>
+      <c r="C51" s="28">
+        <v>1675</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H51" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="I51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K51" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="L51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M51" s="28">
+        <v>3</v>
+      </c>
+      <c r="N51" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="O51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q51" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="R51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T51" s="36">
+        <v>9.7</v>
+      </c>
+      <c r="U51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W51" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="X51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y51" s="28">
+        <v>6</v>
+      </c>
+      <c r="Z51" s="32">
+        <v>14</v>
+      </c>
+      <c r="AA51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC51" s="32">
+        <v>16.6</v>
+      </c>
+      <c r="AD51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF51" s="32">
+        <v>15.2</v>
+      </c>
+      <c r="AG51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH51" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI51" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="AJ51" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK51" s="32">
+        <f>AVERAGE(H51,K51,N51,Q51,T51,W51,Z51,AC51,AF51,AI51)</f>
+      </c>
+      <c r="AL51" s="28">
+        <v>24</v>
+      </c>
+      <c r="AM51" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN51" s="34"/>
+      <c r="AO51" s="35"/>
+      <c r="AP51" s="34"/>
+      <c r="AQ51" s="35"/>
+      <c r="AR51" s="34"/>
+      <c r="AS51" s="35"/>
+      <c r="AT51" s="34"/>
+      <c r="AU51" s="35"/>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B52" s="28">
+        <v>36</v>
+      </c>
+      <c r="C52" s="28">
+        <v>1676</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="28">
+        <v>3</v>
+      </c>
+      <c r="H52" s="32">
+        <v>15.5</v>
+      </c>
+      <c r="I52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K52" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="L52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M52" s="28">
+        <v>6</v>
+      </c>
+      <c r="N52" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="O52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P52" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="R52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T52" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="U52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W52" s="32">
+        <v>16.4</v>
+      </c>
+      <c r="X52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y52" s="28">
+        <v>4</v>
+      </c>
+      <c r="Z52" s="32">
+        <v>10.1</v>
+      </c>
+      <c r="AA52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB52" s="28">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="32">
+        <v>11.2</v>
+      </c>
+      <c r="AD52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE52" s="28">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AG52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH52" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI52" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="AJ52" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK52" s="32">
+        <f>AVERAGE(H52,K52,N52,Q52,T52,W52,Z52,AC52,AF52,AI52)</f>
+      </c>
+      <c r="AL52" s="28">
+        <v>31</v>
+      </c>
+      <c r="AM52" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN52" s="34"/>
+      <c r="AO52" s="35"/>
+      <c r="AP52" s="34"/>
+      <c r="AQ52" s="35"/>
+      <c r="AR52" s="34"/>
+      <c r="AS52" s="35"/>
+      <c r="AT52" s="34"/>
+      <c r="AU52" s="35"/>
+    </row>
+    <row r="53" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B53" s="28">
+        <v>37</v>
+      </c>
+      <c r="C53" s="28">
+        <v>1677</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H53" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="I53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K53" s="32">
+        <v>16.3</v>
+      </c>
+      <c r="L53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N53" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="O53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P53" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q53" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="R53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T53" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="U53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V53" s="28">
+        <v>3</v>
+      </c>
+      <c r="W53" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="X53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z53" s="32">
+        <v>11</v>
+      </c>
+      <c r="AA53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC53" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="AD53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE53" s="28">
+        <v>3</v>
+      </c>
+      <c r="AF53" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="AG53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH53" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI53" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="AJ53" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK53" s="32">
+        <f>AVERAGE(H53,K53,N53,Q53,T53,W53,Z53,AC53,AF53,AI53)</f>
+      </c>
+      <c r="AL53" s="28">
+        <v>28</v>
+      </c>
+      <c r="AM53" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN53" s="34"/>
+      <c r="AO53" s="35"/>
+      <c r="AP53" s="34"/>
+      <c r="AQ53" s="35"/>
+      <c r="AR53" s="34"/>
+      <c r="AS53" s="35"/>
+      <c r="AT53" s="34"/>
+      <c r="AU53" s="35"/>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B54" s="28">
+        <v>38</v>
+      </c>
+      <c r="C54" s="28">
+        <v>1678</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H54" s="32">
+        <v>13</v>
+      </c>
+      <c r="I54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J54" s="28">
+        <v>6</v>
+      </c>
+      <c r="K54" s="32">
+        <v>14.6</v>
+      </c>
+      <c r="L54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M54" s="28">
+        <v>5</v>
+      </c>
+      <c r="N54" s="32">
+        <v>14.3</v>
+      </c>
+      <c r="O54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q54" s="32">
+        <v>14.6</v>
+      </c>
+      <c r="R54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T54" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="U54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V54" s="28">
+        <v>1</v>
+      </c>
+      <c r="W54" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="X54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z54" s="32">
+        <v>10</v>
+      </c>
+      <c r="AA54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC54" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="AD54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF54" s="32">
+        <v>10.9</v>
+      </c>
+      <c r="AG54" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH54" s="28">
+        <v>5</v>
+      </c>
+      <c r="AI54" s="36">
+        <v>8.4</v>
+      </c>
+      <c r="AJ54" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK54" s="32">
+        <f>AVERAGE(H54,K54,N54,Q54,T54,W54,Z54,AC54,AF54,AI54)</f>
+      </c>
+      <c r="AL54" s="28">
+        <v>23</v>
+      </c>
+      <c r="AM54" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN54" s="34"/>
+      <c r="AO54" s="35"/>
+      <c r="AP54" s="34"/>
+      <c r="AQ54" s="35"/>
+      <c r="AR54" s="34"/>
+      <c r="AS54" s="35"/>
+      <c r="AT54" s="34"/>
+      <c r="AU54" s="35"/>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B55" s="28">
+        <v>39</v>
+      </c>
+      <c r="C55" s="28">
+        <v>1679</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H55" s="32">
+        <v>14.6</v>
+      </c>
+      <c r="I55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K55" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="L55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N55" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="O55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q55" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="R55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T55" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="U55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W55" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="X55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z55" s="32">
+        <v>12.6</v>
+      </c>
+      <c r="AA55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB55" s="28">
+        <v>4</v>
+      </c>
+      <c r="AC55" s="32">
+        <v>11.1</v>
+      </c>
+      <c r="AD55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF55" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="AG55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH55" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI55" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AJ55" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK55" s="32">
+        <f>AVERAGE(H55,K55,N55,Q55,T55,W55,Z55,AC55,AF55,AI55)</f>
+      </c>
+      <c r="AL55" s="28">
+        <v>19</v>
+      </c>
+      <c r="AM55" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN55" s="34"/>
+      <c r="AO55" s="35"/>
+      <c r="AP55" s="34"/>
+      <c r="AQ55" s="35"/>
+      <c r="AR55" s="34"/>
+      <c r="AS55" s="35"/>
+      <c r="AT55" s="34"/>
+      <c r="AU55" s="35"/>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B56" s="28">
+        <v>40</v>
+      </c>
+      <c r="C56" s="28">
+        <v>1680</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H56" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="I56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K56" s="32">
+        <v>14</v>
+      </c>
+      <c r="L56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M56" s="28">
+        <v>2</v>
+      </c>
+      <c r="N56" s="32">
+        <v>10.1</v>
+      </c>
+      <c r="O56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P56" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="R56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S56" s="28">
+        <v>5</v>
+      </c>
+      <c r="T56" s="32">
+        <v>15.9</v>
+      </c>
+      <c r="U56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W56" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="X56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z56" s="32">
+        <v>15.5</v>
+      </c>
+      <c r="AA56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB56" s="28">
+        <v>4</v>
+      </c>
+      <c r="AC56" s="32">
+        <v>10</v>
+      </c>
+      <c r="AD56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF56" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="AG56" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH56" s="28">
+        <v>5</v>
+      </c>
+      <c r="AI56" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="AJ56" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK56" s="32">
+        <f>AVERAGE(H56,K56,N56,Q56,T56,W56,Z56,AC56,AF56,AI56)</f>
+      </c>
+      <c r="AL56" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM56" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN56" s="34"/>
+      <c r="AO56" s="35"/>
+      <c r="AP56" s="34"/>
+      <c r="AQ56" s="35"/>
+      <c r="AR56" s="34"/>
+      <c r="AS56" s="35"/>
+      <c r="AT56" s="34"/>
+      <c r="AU56" s="35"/>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B57" s="28">
+        <v>41</v>
+      </c>
+      <c r="C57" s="28">
+        <v>1681</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H57" s="32">
+        <v>10</v>
+      </c>
+      <c r="I57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K57" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="L57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N57" s="32">
+        <v>15.1</v>
+      </c>
+      <c r="O57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q57" s="32">
+        <v>14.9</v>
+      </c>
+      <c r="R57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T57" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="U57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V57" s="28">
+        <v>3</v>
+      </c>
+      <c r="W57" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="X57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y57" s="28">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="AA57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC57" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="AD57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE57" s="28">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="AG57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH57" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI57" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="AJ57" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK57" s="32">
+        <f>AVERAGE(H57,K57,N57,Q57,T57,W57,Z57,AC57,AF57,AI57)</f>
+      </c>
+      <c r="AL57" s="28">
+        <v>22</v>
+      </c>
+      <c r="AM57" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN57" s="34"/>
+      <c r="AO57" s="35"/>
+      <c r="AP57" s="34"/>
+      <c r="AQ57" s="35"/>
+      <c r="AR57" s="34"/>
+      <c r="AS57" s="35"/>
+      <c r="AT57" s="34"/>
+      <c r="AU57" s="35"/>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B58" s="28">
+        <v>42</v>
+      </c>
+      <c r="C58" s="28">
+        <v>1682</v>
+      </c>
+      <c r="D58" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="F58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H58" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="I58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K58" s="32">
+        <v>13</v>
+      </c>
+      <c r="L58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N58" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="O58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q58" s="32">
+        <v>15.3</v>
+      </c>
+      <c r="R58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T58" s="32">
+        <v>13</v>
+      </c>
+      <c r="U58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W58" s="36">
+        <v>9.8</v>
+      </c>
+      <c r="X58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z58" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="AA58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC58" s="32">
+        <v>13.6</v>
+      </c>
+      <c r="AD58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF58" s="32">
+        <v>14.7</v>
+      </c>
+      <c r="AG58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH58" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI58" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="AJ58" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK58" s="32">
+        <f>AVERAGE(H58,K58,N58,Q58,T58,W58,Z58,AC58,AF58,AI58)</f>
+      </c>
+      <c r="AL58" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM58" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN58" s="34"/>
+      <c r="AO58" s="35"/>
+      <c r="AP58" s="34"/>
+      <c r="AQ58" s="35"/>
+      <c r="AR58" s="34"/>
+      <c r="AS58" s="35"/>
+      <c r="AT58" s="34"/>
+      <c r="AU58" s="35"/>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B59" s="28">
+        <v>43</v>
+      </c>
+      <c r="C59" s="28">
+        <v>1683</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H59" s="32">
+        <v>13</v>
+      </c>
+      <c r="I59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K59" s="32">
+        <v>16.3</v>
+      </c>
+      <c r="L59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N59" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="O59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q59" s="32">
+        <v>12</v>
+      </c>
+      <c r="R59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T59" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="U59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W59" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="X59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z59" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="AA59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB59" s="28">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="AD59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF59" s="32">
+        <v>15.1</v>
+      </c>
+      <c r="AG59" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH59" s="28">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="AJ59" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK59" s="32">
+        <f>AVERAGE(H59,K59,N59,Q59,T59,W59,Z59,AC59,AF59,AI59)</f>
+      </c>
+      <c r="AL59" s="28">
+        <v>24</v>
+      </c>
+      <c r="AM59" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN59" s="34"/>
+      <c r="AO59" s="35"/>
+      <c r="AP59" s="34"/>
+      <c r="AQ59" s="35"/>
+      <c r="AR59" s="34"/>
+      <c r="AS59" s="35"/>
+      <c r="AT59" s="34"/>
+      <c r="AU59" s="35"/>
+    </row>
+    <row r="60" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B60" s="28">
+        <v>44</v>
+      </c>
+      <c r="C60" s="28">
+        <v>1684</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H60" s="32">
+        <v>14</v>
+      </c>
+      <c r="I60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K60" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="L60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N60" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="O60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P60" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="R60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S60" s="28">
+        <v>1</v>
+      </c>
+      <c r="T60" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="U60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W60" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="X60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z60" s="36">
+        <v>9.9</v>
+      </c>
+      <c r="AA60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC60" s="32">
+        <v>11.7</v>
+      </c>
+      <c r="AD60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF60" s="32">
+        <v>14</v>
+      </c>
+      <c r="AG60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH60" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI60" s="32">
+        <v>16.9</v>
+      </c>
+      <c r="AJ60" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK60" s="32">
+        <f>AVERAGE(H60,K60,N60,Q60,T60,W60,Z60,AC60,AF60,AI60)</f>
+      </c>
+      <c r="AL60" s="28">
+        <v>18</v>
+      </c>
+      <c r="AM60" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN60" s="34"/>
+      <c r="AO60" s="35"/>
+      <c r="AP60" s="34"/>
+      <c r="AQ60" s="35"/>
+      <c r="AR60" s="34"/>
+      <c r="AS60" s="35"/>
+      <c r="AT60" s="34"/>
+      <c r="AU60" s="35"/>
+    </row>
+    <row r="61" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B61" s="28">
         <v>45</v>
       </c>
-      <c r="H22" s="37">
+      <c r="C61" s="28">
+        <v>1685</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H61" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="I61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J61" s="28">
+        <v>5</v>
+      </c>
+      <c r="K61" s="32">
+        <v>14</v>
+      </c>
+      <c r="L61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N61" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="O61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P61" s="28">
+        <v>4</v>
+      </c>
+      <c r="Q61" s="32">
+        <v>14.9</v>
+      </c>
+      <c r="R61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T61" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="U61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W61" s="32">
+        <v>13.7</v>
+      </c>
+      <c r="X61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z61" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="AA61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC61" s="32">
+        <v>13.7</v>
+      </c>
+      <c r="AD61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF61" s="32">
+        <v>13</v>
+      </c>
+      <c r="AG61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH61" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI61" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="AJ61" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK61" s="32">
+        <f>AVERAGE(H61,K61,N61,Q61,T61,W61,Z61,AC61,AF61,AI61)</f>
+      </c>
+      <c r="AL61" s="28">
+        <v>22</v>
+      </c>
+      <c r="AM61" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN61" s="34"/>
+      <c r="AO61" s="35"/>
+      <c r="AP61" s="34"/>
+      <c r="AQ61" s="35"/>
+      <c r="AR61" s="34"/>
+      <c r="AS61" s="35"/>
+      <c r="AT61" s="34"/>
+      <c r="AU61" s="35"/>
+    </row>
+    <row r="62" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B62" s="28">
+        <v>46</v>
+      </c>
+      <c r="C62" s="28">
+        <v>1686</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H62" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="I62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K62" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="L62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N62" s="36">
+        <v>9.8</v>
+      </c>
+      <c r="O62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q62" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="R62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T62" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="U62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V62" s="28">
+        <v>1</v>
+      </c>
+      <c r="W62" s="36">
+        <v>9.8</v>
+      </c>
+      <c r="X62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y62" s="28">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="32">
+        <v>13</v>
+      </c>
+      <c r="AA62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC62" s="32">
+        <v>12</v>
+      </c>
+      <c r="AD62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE62" s="28">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="AG62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH62" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI62" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="AJ62" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK62" s="32">
+        <f>AVERAGE(H62,K62,N62,Q62,T62,W62,Z62,AC62,AF62,AI62)</f>
+      </c>
+      <c r="AL62" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM62" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN62" s="34"/>
+      <c r="AO62" s="35"/>
+      <c r="AP62" s="34"/>
+      <c r="AQ62" s="35"/>
+      <c r="AR62" s="34"/>
+      <c r="AS62" s="35"/>
+      <c r="AT62" s="34"/>
+      <c r="AU62" s="35"/>
+    </row>
+    <row r="63" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B63" s="28">
+        <v>47</v>
+      </c>
+      <c r="C63" s="28">
+        <v>1687</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H63" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="I63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K63" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="L63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N63" s="32">
+        <v>11.1</v>
+      </c>
+      <c r="O63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P63" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="R63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S63" s="28">
+        <v>3</v>
+      </c>
+      <c r="T63" s="32">
+        <v>10.6</v>
+      </c>
+      <c r="U63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W63" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="X63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z63" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="AA63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC63" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="AD63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF63" s="32">
+        <v>10</v>
+      </c>
+      <c r="AG63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH63" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI63" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="AJ63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK63" s="32">
+        <f>AVERAGE(H63,K63,N63,Q63,T63,W63,Z63,AC63,AF63,AI63)</f>
+      </c>
+      <c r="AL63" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM63" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN63" s="34"/>
+      <c r="AO63" s="35"/>
+      <c r="AP63" s="34"/>
+      <c r="AQ63" s="35"/>
+      <c r="AR63" s="34"/>
+      <c r="AS63" s="35"/>
+      <c r="AT63" s="34"/>
+      <c r="AU63" s="35"/>
+    </row>
+    <row r="64" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B64" s="28">
+        <v>48</v>
+      </c>
+      <c r="C64" s="28">
+        <v>1688</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H64" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="I64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J64" s="28">
+        <v>4</v>
+      </c>
+      <c r="K64" s="32">
+        <v>10.3</v>
+      </c>
+      <c r="L64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N64" s="32">
+        <v>13</v>
+      </c>
+      <c r="O64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q64" s="32">
+        <v>10</v>
+      </c>
+      <c r="R64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T64" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="U64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W64" s="32">
         <v>13.2</v>
       </c>
-      <c r="I22" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="37">
-        <f>AVERAGE(H22)</f>
-      </c>
-      <c r="K22" s="28">
+      <c r="X64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z64" s="32">
+        <v>12</v>
+      </c>
+      <c r="AA64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC64" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="AD64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF64" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="AG64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH64" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI64" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="AJ64" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK64" s="32">
+        <f>AVERAGE(H64,K64,N64,Q64,T64,W64,Z64,AC64,AF64,AI64)</f>
+      </c>
+      <c r="AL64" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM64" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN64" s="34"/>
+      <c r="AO64" s="35"/>
+      <c r="AP64" s="34"/>
+      <c r="AQ64" s="35"/>
+      <c r="AR64" s="34"/>
+      <c r="AS64" s="35"/>
+      <c r="AT64" s="34"/>
+      <c r="AU64" s="35"/>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B65" s="28">
+        <v>49</v>
+      </c>
+      <c r="C65" s="28">
+        <v>1689</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65" s="28">
+        <v>6</v>
+      </c>
+      <c r="H65" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="I65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K65" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="L65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N65" s="32">
+        <v>15.4</v>
+      </c>
+      <c r="O65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q65" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="R65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T65" s="32">
+        <v>16.3</v>
+      </c>
+      <c r="U65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V65" s="28">
+        <v>1</v>
+      </c>
+      <c r="W65" s="32">
+        <v>11</v>
+      </c>
+      <c r="X65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y65" s="28">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="AA65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC65" s="36">
+        <v>9.9</v>
+      </c>
+      <c r="AD65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF65" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="AG65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH65" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI65" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="AJ65" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK65" s="32">
+        <f>AVERAGE(H65,K65,N65,Q65,T65,W65,Z65,AC65,AF65,AI65)</f>
+      </c>
+      <c r="AL65" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM65" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN65" s="34"/>
+      <c r="AO65" s="35"/>
+      <c r="AP65" s="34"/>
+      <c r="AQ65" s="35"/>
+      <c r="AR65" s="34"/>
+      <c r="AS65" s="35"/>
+      <c r="AT65" s="34"/>
+      <c r="AU65" s="35"/>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B66" s="28">
+        <v>50</v>
+      </c>
+      <c r="C66" s="28">
+        <v>1690</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H66" s="32">
+        <v>16</v>
+      </c>
+      <c r="I66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K66" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="L66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N66" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="O66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q66" s="32">
+        <v>11</v>
+      </c>
+      <c r="R66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T66" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="U66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W66" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="X66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z66" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="AA66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB66" s="28">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="AD66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF66" s="32">
+        <v>16.4</v>
+      </c>
+      <c r="AG66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH66" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI66" s="32">
+        <v>14.8</v>
+      </c>
+      <c r="AJ66" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK66" s="32">
+        <f>AVERAGE(H66,K66,N66,Q66,T66,W66,Z66,AC66,AF66,AI66)</f>
+      </c>
+      <c r="AL66" s="28">
         <v>23</v>
       </c>
-      <c r="L22" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M22" s="34"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="35"/>
+      <c r="AM66" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN66" s="34"/>
+      <c r="AO66" s="35"/>
+      <c r="AP66" s="34"/>
+      <c r="AQ66" s="35"/>
+      <c r="AR66" s="34"/>
+      <c r="AS66" s="35"/>
+      <c r="AT66" s="34"/>
+      <c r="AU66" s="35"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
+    <row r="67" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B67" s="28">
         <v>51</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
+      <c r="C67" s="28">
+        <v>1691</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67" s="28">
+        <v>4</v>
+      </c>
+      <c r="H67" s="32">
+        <v>14.9</v>
+      </c>
+      <c r="I67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J67" s="28">
+        <v>3</v>
+      </c>
+      <c r="K67" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="L67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N67" s="32">
+        <v>10</v>
+      </c>
+      <c r="O67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q67" s="32">
+        <v>16.2</v>
+      </c>
+      <c r="R67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T67" s="32">
+        <v>12</v>
+      </c>
+      <c r="U67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V67" s="28">
+        <v>4</v>
+      </c>
+      <c r="W67" s="32">
+        <v>13</v>
+      </c>
+      <c r="X67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y67" s="28">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="32">
+        <v>11.7</v>
+      </c>
+      <c r="AA67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC67" s="32">
+        <v>10.1</v>
+      </c>
+      <c r="AD67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF67" s="32">
+        <v>10.9</v>
+      </c>
+      <c r="AG67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH67" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI67" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="AJ67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK67" s="32">
+        <f>AVERAGE(H67,K67,N67,Q67,T67,W67,Z67,AC67,AF67,AI67)</f>
+      </c>
+      <c r="AL67" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM67" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN67" s="34"/>
+      <c r="AO67" s="35"/>
+      <c r="AP67" s="34"/>
+      <c r="AQ67" s="35"/>
+      <c r="AR67" s="34"/>
+      <c r="AS67" s="35"/>
+      <c r="AT67" s="34"/>
+      <c r="AU67" s="35"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="I27" t="s">
+    <row r="68" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B68" s="28">
+        <v>52</v>
+      </c>
+      <c r="C68" s="28">
+        <v>1692</v>
+      </c>
+      <c r="D68" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H68" s="32">
+        <v>12</v>
+      </c>
+      <c r="I68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J68" s="28">
+        <v>4</v>
+      </c>
+      <c r="K68" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="L68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N68" s="36">
+        <v>9.5</v>
+      </c>
+      <c r="O68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q68" s="32">
+        <v>15.3</v>
+      </c>
+      <c r="R68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T68" s="32">
+        <v>14</v>
+      </c>
+      <c r="U68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W68" s="32">
+        <v>11.5</v>
+      </c>
+      <c r="X68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y68" s="28">
+        <v>3</v>
+      </c>
+      <c r="Z68" s="32">
+        <v>11.4</v>
+      </c>
+      <c r="AA68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB68" s="28">
+        <v>5</v>
+      </c>
+      <c r="AC68" s="32">
+        <v>15.3</v>
+      </c>
+      <c r="AD68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF68" s="32">
+        <v>13.1</v>
+      </c>
+      <c r="AG68" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH68" s="28">
+        <v>1</v>
+      </c>
+      <c r="AI68" s="32">
+        <v>13.7</v>
+      </c>
+      <c r="AJ68" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK68" s="32">
+        <f>AVERAGE(H68,K68,N68,Q68,T68,W68,Z68,AC68,AF68,AI68)</f>
+      </c>
+      <c r="AL68" s="28">
+        <v>27</v>
+      </c>
+      <c r="AM68" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN68" s="34"/>
+      <c r="AO68" s="35"/>
+      <c r="AP68" s="34"/>
+      <c r="AQ68" s="35"/>
+      <c r="AR68" s="34"/>
+      <c r="AS68" s="35"/>
+      <c r="AT68" s="34"/>
+      <c r="AU68" s="35"/>
+    </row>
+    <row r="69" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B69" s="28">
         <v>53</v>
       </c>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
+      <c r="C69" s="28">
+        <v>1693</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H69" s="32">
+        <v>16.5</v>
+      </c>
+      <c r="I69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J69" s="28">
+        <v>2</v>
+      </c>
+      <c r="K69" s="32">
+        <v>16.8</v>
+      </c>
+      <c r="L69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N69" s="36">
+        <v>9.9</v>
+      </c>
+      <c r="O69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P69" s="28">
+        <v>4</v>
+      </c>
+      <c r="Q69" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="R69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T69" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="U69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W69" s="32">
+        <v>15.5</v>
+      </c>
+      <c r="X69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z69" s="32">
+        <v>14</v>
+      </c>
+      <c r="AA69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC69" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="AD69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF69" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="AG69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH69" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI69" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AJ69" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK69" s="32">
+        <f>AVERAGE(H69,K69,N69,Q69,T69,W69,Z69,AC69,AF69,AI69)</f>
+      </c>
+      <c r="AL69" s="28">
+        <v>24</v>
+      </c>
+      <c r="AM69" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN69" s="34"/>
+      <c r="AO69" s="35"/>
+      <c r="AP69" s="34"/>
+      <c r="AQ69" s="35"/>
+      <c r="AR69" s="34"/>
+      <c r="AS69" s="35"/>
+      <c r="AT69" s="34"/>
+      <c r="AU69" s="35"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="41" t="s">
+    <row r="70" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B70" s="28">
         <v>54</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="I28" t="s">
-        <v>54</v>
-      </c>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
+      <c r="C70" s="28">
+        <v>1694</v>
+      </c>
+      <c r="D70" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E70" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="F70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H70" s="32">
+        <v>11.8</v>
+      </c>
+      <c r="I70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K70" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="L70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N70" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="O70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P70" s="28">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="R70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S70" s="28">
+        <v>4</v>
+      </c>
+      <c r="T70" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="U70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V70" s="28">
+        <v>4</v>
+      </c>
+      <c r="W70" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="X70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z70" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AA70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC70" s="36">
+        <v>9.6</v>
+      </c>
+      <c r="AD70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF70" s="32">
+        <v>16.2</v>
+      </c>
+      <c r="AG70" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH70" s="28">
+        <v>6</v>
+      </c>
+      <c r="AI70" s="36">
+        <v>9.8</v>
+      </c>
+      <c r="AJ70" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK70" s="32">
+        <f>AVERAGE(H70,K70,N70,Q70,T70,W70,Z70,AC70,AF70,AI70)</f>
+      </c>
+      <c r="AL70" s="28">
+        <v>19</v>
+      </c>
+      <c r="AM70" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN70" s="34"/>
+      <c r="AO70" s="35"/>
+      <c r="AP70" s="34"/>
+      <c r="AQ70" s="35"/>
+      <c r="AR70" s="34"/>
+      <c r="AS70" s="35"/>
+      <c r="AT70" s="34"/>
+      <c r="AU70" s="35"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
+    <row r="71" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B71" s="28">
+        <v>55</v>
+      </c>
+      <c r="C71" s="28">
+        <v>1695</v>
+      </c>
+      <c r="D71" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E71" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C29" s="42"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="I29" t="s">
-        <v>55</v>
-      </c>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
+      <c r="F71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" s="32">
+        <v>14.9</v>
+      </c>
+      <c r="I71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K71" s="32">
+        <v>10.3</v>
+      </c>
+      <c r="L71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N71" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="O71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P71" s="28">
+        <v>3</v>
+      </c>
+      <c r="Q71" s="32">
+        <v>15</v>
+      </c>
+      <c r="R71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S71" s="28">
+        <v>3</v>
+      </c>
+      <c r="T71" s="32">
+        <v>10.4</v>
+      </c>
+      <c r="U71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W71" s="32">
+        <v>17.2</v>
+      </c>
+      <c r="X71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z71" s="32">
+        <v>14</v>
+      </c>
+      <c r="AA71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC71" s="32">
+        <v>10.4</v>
+      </c>
+      <c r="AD71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE71" s="28">
+        <v>2</v>
+      </c>
+      <c r="AF71" s="32">
+        <v>12.3</v>
+      </c>
+      <c r="AG71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH71" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI71" s="32">
+        <v>12.8</v>
+      </c>
+      <c r="AJ71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK71" s="32">
+        <f>AVERAGE(H71,K71,N71,Q71,T71,W71,Z71,AC71,AF71,AI71)</f>
+      </c>
+      <c r="AL71" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM71" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN71" s="34"/>
+      <c r="AO71" s="35"/>
+      <c r="AP71" s="34"/>
+      <c r="AQ71" s="35"/>
+      <c r="AR71" s="34"/>
+      <c r="AS71" s="35"/>
+      <c r="AT71" s="34"/>
+      <c r="AU71" s="35"/>
+    </row>
+    <row r="72" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B72" s="28">
+        <v>56</v>
+      </c>
+      <c r="C72" s="28">
+        <v>1696</v>
+      </c>
+      <c r="D72" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="32">
+        <v>15.8</v>
+      </c>
+      <c r="I72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J72" s="28">
+        <v>1</v>
+      </c>
+      <c r="K72" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="L72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M72" s="28">
+        <v>2</v>
+      </c>
+      <c r="N72" s="32">
+        <v>13.9</v>
+      </c>
+      <c r="O72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P72" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="R72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T72" s="32">
+        <v>11.9</v>
+      </c>
+      <c r="U72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V72" s="28">
+        <v>6</v>
+      </c>
+      <c r="W72" s="36">
+        <v>9.9</v>
+      </c>
+      <c r="X72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z72" s="32">
+        <v>13</v>
+      </c>
+      <c r="AA72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC72" s="32">
+        <v>13.8</v>
+      </c>
+      <c r="AD72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE72" s="28">
+        <v>2</v>
+      </c>
+      <c r="AF72" s="32">
+        <v>14.7</v>
+      </c>
+      <c r="AG72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH72" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI72" s="36">
+        <v>9.6</v>
+      </c>
+      <c r="AJ72" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK72" s="32">
+        <f>AVERAGE(H72,K72,N72,Q72,T72,W72,Z72,AC72,AF72,AI72)</f>
+      </c>
+      <c r="AL72" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM72" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN72" s="34"/>
+      <c r="AO72" s="35"/>
+      <c r="AP72" s="34"/>
+      <c r="AQ72" s="35"/>
+      <c r="AR72" s="34"/>
+      <c r="AS72" s="35"/>
+      <c r="AT72" s="34"/>
+      <c r="AU72" s="35"/>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B73" s="28">
+        <v>57</v>
+      </c>
+      <c r="C73" s="28">
+        <v>1697</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H73" s="36">
+        <v>9.5</v>
+      </c>
+      <c r="I73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J73" s="28">
+        <v>6</v>
+      </c>
+      <c r="K73" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="L73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N73" s="32">
+        <v>10</v>
+      </c>
+      <c r="O73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P73" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q73" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="R73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T73" s="32">
+        <v>10.5</v>
+      </c>
+      <c r="U73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W73" s="32">
+        <v>12.1</v>
+      </c>
+      <c r="X73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y73" s="28">
+        <v>4</v>
+      </c>
+      <c r="Z73" s="32">
+        <v>10.2</v>
+      </c>
+      <c r="AA73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB73" s="28">
+        <v>3</v>
+      </c>
+      <c r="AC73" s="32">
+        <v>14</v>
+      </c>
+      <c r="AD73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF73" s="32">
+        <v>11.7</v>
+      </c>
+      <c r="AG73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH73" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI73" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="AJ73" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK73" s="32">
+        <f>AVERAGE(H73,K73,N73,Q73,T73,W73,Z73,AC73,AF73,AI73)</f>
+      </c>
+      <c r="AL73" s="28">
+        <v>22</v>
+      </c>
+      <c r="AM73" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN73" s="34"/>
+      <c r="AO73" s="35"/>
+      <c r="AP73" s="34"/>
+      <c r="AQ73" s="35"/>
+      <c r="AR73" s="34"/>
+      <c r="AS73" s="35"/>
+      <c r="AT73" s="34"/>
+      <c r="AU73" s="35"/>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B74" s="28">
+        <v>58</v>
+      </c>
+      <c r="C74" s="28">
+        <v>1698</v>
+      </c>
+      <c r="D74" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="32">
+        <v>12</v>
+      </c>
+      <c r="I74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J74" s="28">
+        <v>3</v>
+      </c>
+      <c r="K74" s="32">
+        <v>12.5</v>
+      </c>
+      <c r="L74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M74" s="28">
+        <v>1</v>
+      </c>
+      <c r="N74" s="36">
+        <v>8.3</v>
+      </c>
+      <c r="O74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q74" s="36">
+        <v>8.9</v>
+      </c>
+      <c r="R74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T74" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="U74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W74" s="32">
+        <v>14.5</v>
+      </c>
+      <c r="X74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z74" s="32">
+        <v>13.3</v>
+      </c>
+      <c r="AA74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB74" s="28">
+        <v>6</v>
+      </c>
+      <c r="AC74" s="32">
+        <v>10.4</v>
+      </c>
+      <c r="AD74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF74" s="32">
+        <v>11.3</v>
+      </c>
+      <c r="AG74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI74" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="AJ74" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK74" s="32">
+        <f>AVERAGE(H74,K74,N74,Q74,T74,W74,Z74,AC74,AF74,AI74)</f>
+      </c>
+      <c r="AL74" s="28">
+        <v>21</v>
+      </c>
+      <c r="AM74" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN74" s="34"/>
+      <c r="AO74" s="35"/>
+      <c r="AP74" s="34"/>
+      <c r="AQ74" s="35"/>
+      <c r="AR74" s="34"/>
+      <c r="AS74" s="35"/>
+      <c r="AT74" s="34"/>
+      <c r="AU74" s="35"/>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B75" s="28">
+        <v>59</v>
+      </c>
+      <c r="C75" s="28">
+        <v>1714</v>
+      </c>
+      <c r="D75" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E75" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H75" s="32">
+        <v>14.2</v>
+      </c>
+      <c r="I75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="K75" s="32">
+        <v>17.1</v>
+      </c>
+      <c r="L75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N75" s="32">
+        <v>11.2</v>
+      </c>
+      <c r="O75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q75" s="36">
+        <v>9.3</v>
+      </c>
+      <c r="R75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S75" s="28">
+        <v>1</v>
+      </c>
+      <c r="T75" s="32">
+        <v>13</v>
+      </c>
+      <c r="U75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W75" s="32">
+        <v>12.4</v>
+      </c>
+      <c r="X75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z75" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="AA75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB75" s="28">
+        <v>3</v>
+      </c>
+      <c r="AC75" s="36">
+        <v>9.1</v>
+      </c>
+      <c r="AD75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF75" s="32">
+        <v>14.7</v>
+      </c>
+      <c r="AG75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI75" s="32">
+        <v>14</v>
+      </c>
+      <c r="AJ75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK75" s="32">
+        <f>AVERAGE(H75,K75,N75,Q75,T75,W75,Z75,AC75,AF75,AI75)</f>
+      </c>
+      <c r="AL75" s="28">
+        <v>30</v>
+      </c>
+      <c r="AM75" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN75" s="34"/>
+      <c r="AO75" s="35"/>
+      <c r="AP75" s="34"/>
+      <c r="AQ75" s="35"/>
+      <c r="AR75" s="34"/>
+      <c r="AS75" s="35"/>
+      <c r="AT75" s="34"/>
+      <c r="AU75" s="35"/>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B76" s="28">
+        <v>60</v>
+      </c>
+      <c r="C76" s="28">
+        <v>1749</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="28">
+        <v>4</v>
+      </c>
+      <c r="H76" s="32">
+        <v>12</v>
+      </c>
+      <c r="I76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J76" s="28">
+        <v>5</v>
+      </c>
+      <c r="K76" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="L76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N76" s="32">
+        <v>12.9</v>
+      </c>
+      <c r="O76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q76" s="32">
+        <v>12.2</v>
+      </c>
+      <c r="R76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T76" s="36">
+        <v>9.3</v>
+      </c>
+      <c r="U76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V76" s="28">
+        <v>2</v>
+      </c>
+      <c r="W76" s="32">
+        <v>16.3</v>
+      </c>
+      <c r="X76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z76" s="32">
+        <v>14.1</v>
+      </c>
+      <c r="AA76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB76" s="28">
+        <v>6</v>
+      </c>
+      <c r="AC76" s="32">
+        <v>13.5</v>
+      </c>
+      <c r="AD76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE76" s="28">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="AG76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH76" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI76" s="32">
+        <v>13.2</v>
+      </c>
+      <c r="AJ76" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK76" s="32">
+        <f>AVERAGE(H76,K76,N76,Q76,T76,W76,Z76,AC76,AF76,AI76)</f>
+      </c>
+      <c r="AL76" s="28">
+        <v>20</v>
+      </c>
+      <c r="AM76" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN76" s="34"/>
+      <c r="AO76" s="35"/>
+      <c r="AP76" s="34"/>
+      <c r="AQ76" s="35"/>
+      <c r="AR76" s="34"/>
+      <c r="AS76" s="35"/>
+      <c r="AT76" s="34"/>
+      <c r="AU76" s="35"/>
+    </row>
+    <row r="77" ht="20" customHeight="1" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B77" s="28">
+        <v>61</v>
+      </c>
+      <c r="C77" s="28">
+        <v>1761</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="G77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H77" s="32">
+        <v>10.8</v>
+      </c>
+      <c r="I77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J77" s="28">
+        <v>4</v>
+      </c>
+      <c r="K77" s="32">
+        <v>13.4</v>
+      </c>
+      <c r="L77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="N77" s="32">
+        <v>14</v>
+      </c>
+      <c r="O77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="P77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q77" s="32">
+        <v>10.9</v>
+      </c>
+      <c r="R77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="S77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="T77" s="32">
+        <v>14.4</v>
+      </c>
+      <c r="U77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="V77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W77" s="32">
+        <v>10.7</v>
+      </c>
+      <c r="X77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z77" s="32">
+        <v>15.6</v>
+      </c>
+      <c r="AA77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC77" s="32">
+        <v>11.7</v>
+      </c>
+      <c r="AD77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF77" s="32">
+        <v>12.7</v>
+      </c>
+      <c r="AG77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH77" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI77" s="32">
+        <v>12.6</v>
+      </c>
+      <c r="AJ77" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK77" s="32">
+        <f>AVERAGE(H77,K77,N77,Q77,T77,W77,Z77,AC77,AF77,AI77)</f>
+      </c>
+      <c r="AL77" s="28">
+        <v>22</v>
+      </c>
+      <c r="AM77" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN77" s="34"/>
+      <c r="AO77" s="35"/>
+      <c r="AP77" s="34"/>
+      <c r="AQ77" s="35"/>
+      <c r="AR77" s="34"/>
+      <c r="AS77" s="35"/>
+      <c r="AT77" s="34"/>
+      <c r="AU77" s="35"/>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B79" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+    </row>
+    <row r="82" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B82" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="39"/>
+      <c r="F82" s="39"/>
+      <c r="U82" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="V82" s="39"/>
+      <c r="W82" s="39"/>
+      <c r="X82" s="39"/>
+      <c r="Y82" s="39"/>
+      <c r="Z82" s="39"/>
+      <c r="AA82" s="39"/>
+      <c r="AB82" s="39"/>
+      <c r="AC82" s="39"/>
+      <c r="AD82" s="39"/>
+      <c r="AE82" s="39"/>
+      <c r="AF82" s="39"/>
+      <c r="AG82" s="39"/>
+      <c r="AH82" s="39"/>
+      <c r="AI82" s="39"/>
+      <c r="AJ82" s="39"/>
+    </row>
+    <row r="83" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B83" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="U83" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="V83" s="40"/>
+      <c r="W83" s="40"/>
+      <c r="X83" s="40"/>
+      <c r="Y83" s="40"/>
+      <c r="Z83" s="40"/>
+      <c r="AA83" s="40"/>
+      <c r="AB83" s="40"/>
+      <c r="AC83" s="40"/>
+      <c r="AD83" s="40"/>
+      <c r="AE83" s="40"/>
+      <c r="AF83" s="40"/>
+      <c r="AG83" s="40"/>
+      <c r="AH83" s="40"/>
+      <c r="AI83" s="40"/>
+      <c r="AJ83" s="40"/>
+    </row>
+    <row r="84" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B84" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="41"/>
+      <c r="F84" s="41"/>
+      <c r="U84" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="V84" s="41"/>
+      <c r="W84" s="41"/>
+      <c r="X84" s="41"/>
+      <c r="Y84" s="41"/>
+      <c r="Z84" s="41"/>
+      <c r="AA84" s="41"/>
+      <c r="AB84" s="41"/>
+      <c r="AC84" s="41"/>
+      <c r="AD84" s="41"/>
+      <c r="AE84" s="41"/>
+      <c r="AF84" s="41"/>
+      <c r="AG84" s="41"/>
+      <c r="AH84" s="41"/>
+      <c r="AI84" s="41"/>
+      <c r="AJ84" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="74">
     <mergeCell ref="D2:R4"/>
-    <mergeCell ref="B5:T5"/>
+    <mergeCell ref="B5:AU5"/>
     <mergeCell ref="B7:R7"/>
     <mergeCell ref="B8:R8"/>
     <mergeCell ref="B10:D10"/>
@@ -1654,36 +9440,63 @@
     <mergeCell ref="O12:R12"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="F14:H14"/>
-    <mergeCell ref="M14:T14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="AA14:AC14"/>
+    <mergeCell ref="AD14:AF14"/>
+    <mergeCell ref="AG14:AI14"/>
+    <mergeCell ref="AN14:AU14"/>
     <mergeCell ref="B14:B16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="E14:E16"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="K14:K16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="L15:M15"/>
     <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AD15:AE15"/>
+    <mergeCell ref="AG15:AH15"/>
+    <mergeCell ref="AJ14:AJ16"/>
+    <mergeCell ref="AK14:AK16"/>
+    <mergeCell ref="AL14:AL16"/>
+    <mergeCell ref="AM14:AM16"/>
+    <mergeCell ref="AN15:AO15"/>
+    <mergeCell ref="AP15:AQ15"/>
+    <mergeCell ref="AR15:AS15"/>
+    <mergeCell ref="AT15:AU15"/>
     <mergeCell ref="H15:H16"/>
-    <mergeCell ref="M17:M22"/>
-    <mergeCell ref="N17:N22"/>
-    <mergeCell ref="O17:O22"/>
-    <mergeCell ref="P17:P22"/>
-    <mergeCell ref="Q17:Q22"/>
-    <mergeCell ref="R17:R22"/>
-    <mergeCell ref="S17:S22"/>
-    <mergeCell ref="T17:T22"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AC15:AC16"/>
+    <mergeCell ref="AF15:AF16"/>
+    <mergeCell ref="AI15:AI16"/>
+    <mergeCell ref="AN17:AN77"/>
+    <mergeCell ref="AO17:AO77"/>
+    <mergeCell ref="AP17:AP77"/>
+    <mergeCell ref="AQ17:AQ77"/>
+    <mergeCell ref="AR17:AR77"/>
+    <mergeCell ref="AS17:AS77"/>
+    <mergeCell ref="AT17:AT77"/>
+    <mergeCell ref="AU17:AU77"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="U82:AJ82"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="U83:AJ83"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="U84:AJ84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
